--- a/today_issues.xlsx
+++ b/today_issues.xlsx
@@ -421,313 +421,313 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Y-BUG-026</v>
+        <v>Y-BUG-021</v>
       </c>
       <c r="B2" t="str">
-        <v>测试用例不足</v>
+        <v>用户密码重置功能存在安全漏洞，重置链接未设置过期时间，可能被恶意利用，需要添加token有效期验证</v>
       </c>
       <c r="C2" t="str">
-        <v>孙八</v>
+        <v>赵六</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-22</v>
       </c>
       <c r="E2" t="str">
-        <v>严重</v>
+        <v>致命</v>
       </c>
       <c r="F2" t="str">
-        <v>根因：支付功能异常，预计解决时间：2026-04-26</v>
+        <v>该问题已在测试环境复现，正在编写修复方案</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Y-BUG-019</v>
+        <v>Y-BUG-015</v>
       </c>
       <c r="B3" t="str">
-        <v>权限问题</v>
+        <v>CI/CD部署失败，Docker镜像构建超时，需要优化构建脚本和依赖下载速度</v>
       </c>
       <c r="C3" t="str">
-        <v>郑一</v>
+        <v>赵六</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E3" t="str">
-        <v>提示</v>
+        <v>严重</v>
       </c>
       <c r="F3" t="str">
-        <v>根因：安全漏洞，预计解决时间：2026-04-26</v>
+        <v>代码review已通过，等待合并到主分支</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Y-BUG-100</v>
+        <v>Y-BUG-038</v>
       </c>
       <c r="B4" t="str">
-        <v>配置错误</v>
+        <v>用户密码重置功能存在安全漏洞，重置链接未设置过期时间，可能被恶意利用，需要添加token有效期验证</v>
       </c>
       <c r="C4" t="str">
-        <v>陈三</v>
+        <v>孙八</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E4" t="str">
         <v>严重</v>
       </c>
       <c r="F4" t="str">
-        <v>根因：功能模块缺失，预计解决时间：2026-04-26</v>
+        <v>需要与产品确认需求细节，当前需求描述不够清晰</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Y-BUG-082</v>
+        <v>Y-BUG-006</v>
       </c>
       <c r="B5" t="str">
-        <v>性能问题</v>
+        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
       </c>
       <c r="C5" t="str">
-        <v>周九</v>
+        <v>林四</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E5" t="str">
-        <v>致命</v>
+        <v>严重</v>
       </c>
       <c r="F5" t="str">
-        <v>根因：测试用例不足，预计解决时间：2026-04-26</v>
+        <v>代码review已通过，等待合并到主分支</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Y-BUG-052</v>
+        <v>Y-BUG-043</v>
       </c>
       <c r="B6" t="str">
-        <v>文档缺失</v>
+        <v>数据库连接池在高并发场景下出现连接耗尽，需要增加连接池最大连接数配置和连接回收机制</v>
       </c>
       <c r="C6" t="str">
-        <v>孙八</v>
+        <v>吴十</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-15</v>
+        <v>2026-05-01</v>
       </c>
       <c r="E6" t="str">
-        <v>严重</v>
+        <v>一般</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>需要与产品确认需求细节，当前需求描述不够清晰。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Y-BUG-045</v>
+        <v>Y-BUG-031</v>
       </c>
       <c r="B7" t="str">
-        <v>权限问题</v>
+        <v>订单状态流转逻辑错误，已取消的订单仍能继续支付，需要修复状态机转换规则</v>
       </c>
       <c r="C7" t="str">
-        <v>林四</v>
+        <v>杨八</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E7" t="str">
-        <v>一般</v>
+        <v>严重</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>【pending】该问题已在测试环境复现，正在编写修复方案。代码review已通过，等待合并到主分支。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Y-BUG-038</v>
+        <v>Y-BUG-044</v>
       </c>
       <c r="B8" t="str">
-        <v>异常处理缺失</v>
+        <v>iOS端App在iOS 15以下版本兼容性问题，某些功能按钮点击无响应，需要检查事件绑定方式</v>
       </c>
       <c r="C8" t="str">
-        <v>张三</v>
+        <v>赵六</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E8" t="str">
         <v>严重</v>
       </c>
       <c r="F8" t="str">
-        <v>根因：登录页面崩溃，预计解决时间：2026-04-26</v>
+        <v>【长期跟踪】需要与产品确认需求细节，当前需求描述不够清晰。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Y-BUG-058</v>
+        <v>Y-BUG-005</v>
       </c>
       <c r="B9" t="str">
-        <v>代码冗余</v>
+        <v>用户反馈弹窗关闭按钮位置不合理，用户容易误触，需要优化UI布局和交互体验</v>
       </c>
       <c r="C9" t="str">
-        <v>郑一</v>
+        <v>陈七</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-29</v>
       </c>
       <c r="E9" t="str">
         <v>提示</v>
       </c>
       <c r="F9" t="str">
-        <v>根因：性能问题，预计解决时间：2026-04-26</v>
+        <v>【deferred】需要与产品确认需求细节，当前需求描述不够清晰。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-08</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Y-BUG-068</v>
+        <v>Y-BUG-048</v>
       </c>
       <c r="B10" t="str">
-        <v>性能问题</v>
+        <v>报表导出功能模块缺失，用户无法导出Excel格式的统计报表，需要新增导出功能组件和后端接口</v>
       </c>
       <c r="C10" t="str">
-        <v>郑一</v>
+        <v>林四</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-22</v>
       </c>
       <c r="E10" t="str">
         <v>严重</v>
       </c>
       <c r="F10" t="str">
-        <v>根因：功能模块缺失，预计解决时间：2026-04-26</v>
+        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计需要2个开发工作日完成修复，包含测试和回归验证。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Y-BUG-033</v>
+        <v>Y-BUG-019</v>
       </c>
       <c r="B11" t="str">
-        <v>代码冗余</v>
+        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
       </c>
       <c r="C11" t="str">
         <v>孙八</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E11" t="str">
-        <v>致命</v>
+        <v>提示</v>
       </c>
       <c r="F11" t="str">
-        <v>[长期跟踪] 根因：性能问题，预计解决时间：2026-04-26</v>
+        <v>需要与产品确认需求细节，当前需求描述不够清晰。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Y-BUG-080</v>
+        <v>Y-BUG-022</v>
       </c>
       <c r="B12" t="str">
-        <v>缓存失效</v>
+        <v>测试用例覆盖率不足60%，核心功能缺少单元测试，需要补充测试用例确保代码质量</v>
       </c>
       <c r="C12" t="str">
-        <v>杨八</v>
+        <v>郑一</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-29</v>
       </c>
       <c r="E12" t="str">
-        <v>提示</v>
+        <v>致命</v>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>【长期跟踪】该问题是已知问题，已列入后续迭代计划。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Y-BUG-048</v>
+        <v>Y-BUG-032</v>
       </c>
       <c r="B13" t="str">
-        <v>性能问题</v>
+        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
       </c>
       <c r="C13" t="str">
-        <v>陈三</v>
+        <v>陈七</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E13" t="str">
         <v>提示</v>
       </c>
       <c r="F13" t="str">
-        <v>根因：数据加载失败，预计解决时间：2026-04-26</v>
+        <v>【暂不处理】涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Y-BUG-003</v>
+        <v>Y-BUG-009</v>
       </c>
       <c r="B14" t="str">
-        <v>用户体验优化</v>
+        <v>首页数据加载失败，显示空白页面，经检查是接口返回数据格式变更导致JSON解析错误，需要更新数据解析逻辑</v>
       </c>
       <c r="C14" t="str">
-        <v>钱七</v>
+        <v>周九</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E14" t="str">
         <v>致命</v>
       </c>
       <c r="F14" t="str">
-        <v>[pending] 根因：功能模块缺失，预计解决时间：2026-04-26</v>
+        <v>代码review已通过，等待合并到主分支。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Y-BUG-042</v>
+        <v>Y-BUG-008</v>
       </c>
       <c r="B15" t="str">
-        <v>缓存失效</v>
+        <v>支付功能在移动端提交订单时出现网络超时错误，经排查发现是API请求超时时间设置过短，需要调整axios的timeout配置</v>
       </c>
       <c r="C15" t="str">
-        <v>黄五</v>
+        <v>王五</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E15" t="str">
-        <v>一般</v>
+        <v>提示</v>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>【跟踪中】已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计需要2个开发工作日完成修复，包含测试和回归验证。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Y-BUG-062</v>
+        <v>Y-BUG-012</v>
       </c>
       <c r="B16" t="str">
-        <v>测试用例不足</v>
+        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
       </c>
       <c r="C16" t="str">
-        <v>陈七</v>
+        <v>李四</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E16" t="str">
-        <v>严重</v>
+        <v>一般</v>
       </c>
       <c r="F16" t="str">
-        <v>[deferred] 根因：异常处理缺失，预计解决时间：2026-04-26</v>
+        <v>【跟踪中】需要升级依赖库版本，但可能影响其他模块，需要评估风险。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-09</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Y-BUG-060</v>
+        <v>Y-BUG-025</v>
       </c>
       <c r="B17" t="str">
-        <v>功能模块缺失</v>
+        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
       </c>
       <c r="C17" t="str">
-        <v>林四</v>
+        <v>刘六</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-25</v>
@@ -736,67 +736,67 @@
         <v>提示</v>
       </c>
       <c r="F17" t="str">
-        <v>[pending] 根因：文档缺失，预计解决时间：2026-04-26</v>
+        <v>【暂不处理】已经定位到问题根因，是由于异步请求时序问题导致状态不一致。已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计解决时间：2026-05-09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Y-BUG-016</v>
+        <v>Y-BUG-007</v>
       </c>
       <c r="B18" t="str">
-        <v>安全漏洞</v>
+        <v>支付功能在移动端提交订单时出现网络超时错误，经排查发现是API请求超时时间设置过短，需要调整axios的timeout配置</v>
       </c>
       <c r="C18" t="str">
         <v>陈七</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E18" t="str">
-        <v>提示</v>
+        <v>严重</v>
       </c>
       <c r="F18" t="str">
-        <v>[pending] 根因：异常处理缺失，预计解决时间：2026-04-26</v>
+        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Y-BUG-066</v>
+        <v>Y-BUG-039</v>
       </c>
       <c r="B19" t="str">
-        <v>界面样式错乱</v>
+        <v>Redis缓存失效导致频繁查询数据库，需要检查缓存更新策略和过期时间设置</v>
       </c>
       <c r="C19" t="str">
-        <v>吴十</v>
+        <v>钱七</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E19" t="str">
-        <v>严重</v>
+        <v>提示</v>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>代码review已通过，等待合并到主分支</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Y-BUG-076</v>
+        <v>Y-BUG-020</v>
       </c>
       <c r="B20" t="str">
-        <v>异常处理缺失</v>
+        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
       </c>
       <c r="C20" t="str">
-        <v>王五</v>
+        <v>刘六</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-22</v>
       </c>
       <c r="E20" t="str">
         <v>严重</v>
       </c>
       <c r="F20" t="str">
-        <v>[deferred] 根因：缓存失效，预计解决时间：2026-04-26</v>
+        <v>【pending】经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-06</v>
       </c>
     </row>
     <row r="21">
@@ -804,59 +804,59 @@
         <v>Y-BUG-050</v>
       </c>
       <c r="B21" t="str">
-        <v>异常处理缺失</v>
+        <v>首页数据加载失败，显示空白页面，经检查是接口返回数据格式变更导致JSON解析错误，需要更新数据解析逻辑</v>
       </c>
       <c r="C21" t="str">
-        <v>钱七</v>
+        <v>张三</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E21" t="str">
-        <v>致命</v>
+        <v>提示</v>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>预计需要2个开发工作日完成修复，包含测试和回归验证。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Y-BUG-078</v>
+        <v>Y-BUG-045</v>
       </c>
       <c r="B22" t="str">
-        <v>部署失败</v>
+        <v>用户注册API接口返回400错误，参数验证失败，需要检查请求参数格式和后端验证逻辑是否匹配</v>
       </c>
       <c r="C22" t="str">
-        <v>赵六</v>
+        <v>周九</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E22" t="str">
-        <v>一般</v>
+        <v>致命</v>
       </c>
       <c r="F22" t="str">
-        <v/>
+        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Y-BUG-079</v>
+        <v>Y-BUG-046</v>
       </c>
       <c r="B23" t="str">
-        <v>测试用例不足</v>
+        <v>报表导出功能模块缺失，用户无法导出Excel格式的统计报表，需要新增导出功能组件和后端接口</v>
       </c>
       <c r="C23" t="str">
-        <v>林四</v>
+        <v>钱七</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-22</v>
       </c>
       <c r="E23" t="str">
-        <v>致命</v>
+        <v>提示</v>
       </c>
       <c r="F23" t="str">
-        <v>[pending] 根因：异常处理缺失，预计解决时间：2026-04-26</v>
+        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="24">
@@ -864,950 +864,950 @@
         <v>Y-BUG-004</v>
       </c>
       <c r="B24" t="str">
-        <v>配置错误</v>
+        <v>配置文件管理混乱，开发环境和生产环境配置混用，需要建立统一的配置管理方案</v>
       </c>
       <c r="C24" t="str">
-        <v>郑一</v>
+        <v>王五</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E24" t="str">
-        <v>致命</v>
+        <v>提示</v>
       </c>
       <c r="F24" t="str">
-        <v>根因：文档缺失，预计解决时间：2026-04-26</v>
+        <v>预计需要2个开发工作日完成修复，包含测试和回归验证</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Y-BUG-054</v>
+        <v>Y-BUG-003</v>
       </c>
       <c r="B25" t="str">
-        <v>界面样式错乱</v>
+        <v>用户列表页面在小屏幕设备上样式错乱，表格列重叠，需要优化响应式布局和媒体查询设置</v>
       </c>
       <c r="C25" t="str">
         <v>李四</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-17</v>
+        <v>2026-05-01</v>
       </c>
       <c r="E25" t="str">
-        <v>致命</v>
+        <v>严重</v>
       </c>
       <c r="F25" t="str">
-        <v/>
+        <v>预计需要2个开发工作日完成修复，包含测试和回归验证。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Y-BUG-034</v>
+        <v>Y-BUG-030</v>
       </c>
       <c r="B26" t="str">
-        <v>代码冗余</v>
+        <v>报表导出功能模块缺失，用户无法导出Excel格式的统计报表，需要新增导出功能组件和后端接口</v>
       </c>
       <c r="C26" t="str">
-        <v>吴十</v>
+        <v>李四</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-22</v>
       </c>
       <c r="E26" t="str">
-        <v>致命</v>
+        <v>严重</v>
       </c>
       <c r="F26" t="str">
-        <v/>
+        <v>【长期跟踪】该问题已在测试环境复现，正在编写修复方案。需要升级依赖库版本，但可能影响其他模块，需要评估风险。预计解决时间：2026-05-09</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Y-BUG-086</v>
+        <v>Y-BUG-010</v>
       </c>
       <c r="B27" t="str">
-        <v>测试用例不足</v>
+        <v>测试用例覆盖率不足60%，核心功能缺少单元测试，需要补充测试用例确保代码质量</v>
       </c>
       <c r="C27" t="str">
-        <v>郑一</v>
+        <v>林四</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E27" t="str">
         <v>严重</v>
       </c>
       <c r="F27" t="str">
-        <v>[pending] 根因：异常处理缺失，预计解决时间：2026-04-26</v>
+        <v>需要与产品确认需求细节，当前需求描述不够清晰</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Y-BUG-051</v>
+        <v>Y-BUG-014</v>
       </c>
       <c r="B28" t="str">
-        <v>API接口错误</v>
+        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
       </c>
       <c r="C28" t="str">
-        <v>李四</v>
+        <v>刘六</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E28" t="str">
-        <v>提示</v>
+        <v>致命</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Y-BUG-064</v>
+        <v>Y-BUG-011</v>
       </c>
       <c r="B29" t="str">
-        <v>数据加载失败</v>
+        <v>测试用例覆盖率不足60%，核心功能缺少单元测试，需要补充测试用例确保代码质量</v>
       </c>
       <c r="C29" t="str">
-        <v>黄五</v>
+        <v>赵六</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E29" t="str">
         <v>提示</v>
       </c>
       <c r="F29" t="str">
-        <v>[pending] 根因：缓存失效，预计解决时间：2026-04-26</v>
+        <v>【长期跟踪】该问题是已知问题，已列入后续迭代计划。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Y-BUG-014</v>
+        <v>Y-BUG-002</v>
       </c>
       <c r="B30" t="str">
-        <v>登录页面崩溃</v>
+        <v>用户密码重置功能存在安全漏洞，重置链接未设置过期时间，可能被恶意利用，需要添加token有效期验证</v>
       </c>
       <c r="C30" t="str">
-        <v>陈七</v>
+        <v>陈三</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E30" t="str">
-        <v>提示</v>
+        <v>致命</v>
       </c>
       <c r="F30" t="str">
-        <v>根因：用户体验优化，预计解决时间：2026-04-26</v>
+        <v>该问题是已知问题，已列入后续迭代计划。需要升级依赖库版本，但可能影响其他模块，需要评估风险。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Y-BUG-047</v>
+        <v>Y-BUG-037</v>
       </c>
       <c r="B31" t="str">
-        <v>性能问题</v>
+        <v>测试用例覆盖率不足60%，核心功能缺少单元测试，需要补充测试用例确保代码质量</v>
       </c>
       <c r="C31" t="str">
-        <v>李四</v>
+        <v>钱七</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E31" t="str">
-        <v>提示</v>
+        <v>一般</v>
       </c>
       <c r="F31" t="str">
-        <v/>
+        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Y-BUG-022</v>
+        <v>Y-BUG-035</v>
       </c>
       <c r="B32" t="str">
-        <v>数据库连接失败</v>
+        <v>用户权限验证逻辑存在漏洞，普通用户可以访问管理员页面，需要加强路由守卫和权限检查</v>
       </c>
       <c r="C32" t="str">
-        <v>孙八</v>
+        <v>黄五</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E32" t="str">
         <v>一般</v>
       </c>
       <c r="F32" t="str">
-        <v/>
+        <v>【pending】经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-08</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Y-BUG-012</v>
+        <v>Y-BUG-026</v>
       </c>
       <c r="B33" t="str">
-        <v>代码冗余</v>
+        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
       </c>
       <c r="C33" t="str">
-        <v>吴十</v>
+        <v>钱七</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E33" t="str">
-        <v>致命</v>
+        <v>提示</v>
       </c>
       <c r="F33" t="str">
-        <v>根因：安全漏洞，预计解决时间：2026-04-26</v>
+        <v>【暂不处理】需要与产品确认需求细节，当前需求描述不够清晰。已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计解决时间：2026-05-09</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Y-BUG-099</v>
+        <v>Y-BUG-027</v>
       </c>
       <c r="B34" t="str">
-        <v>安全漏洞</v>
+        <v>用户列表页面在小屏幕设备上样式错乱，表格列重叠，需要优化响应式布局和媒体查询设置</v>
       </c>
       <c r="C34" t="str">
-        <v>孙八</v>
+        <v>陈七</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-24</v>
+        <v>2026-05-01</v>
       </c>
       <c r="E34" t="str">
-        <v>一般</v>
+        <v>提示</v>
       </c>
       <c r="F34" t="str">
-        <v>根因：测试用例不足，预计解决时间：2026-04-26</v>
+        <v>代码review已通过，等待合并到主分支</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Y-BUG-023</v>
+        <v>Y-BUG-017</v>
       </c>
       <c r="B35" t="str">
-        <v>测试用例不足</v>
+        <v>报表导出功能模块缺失，用户无法导出Excel格式的统计报表，需要新增导出功能组件和后端接口</v>
       </c>
       <c r="C35" t="str">
-        <v>王二</v>
+        <v>张三</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E35" t="str">
-        <v>提示</v>
+        <v>一般</v>
       </c>
       <c r="F35" t="str">
-        <v/>
+        <v>该问题已在测试环境复现，正在编写修复方案</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Y-BUG-029</v>
+        <v>Y-BUG-040</v>
       </c>
       <c r="B36" t="str">
-        <v>缓存失效</v>
+        <v>支付功能在移动端提交订单时出现网络超时错误，经排查发现是API请求超时时间设置过短，需要调整axios的timeout配置</v>
       </c>
       <c r="C36" t="str">
-        <v>林四</v>
+        <v>刘六</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E36" t="str">
-        <v>严重</v>
+        <v>提示</v>
       </c>
       <c r="F36" t="str">
-        <v>根因：部署失败，预计解决时间：2026-04-26</v>
+        <v>【长期跟踪】代码review已通过，等待合并到主分支。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-07</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Y-BUG-075</v>
+        <v>Y-BUG-029</v>
       </c>
       <c r="B37" t="str">
-        <v>代码冗余</v>
+        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
       </c>
       <c r="C37" t="str">
-        <v>周九</v>
+        <v>孙八</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-15</v>
+        <v>2026-05-01</v>
       </c>
       <c r="E37" t="str">
-        <v>一般</v>
+        <v>致命</v>
       </c>
       <c r="F37" t="str">
-        <v>根因：异常处理缺失，预计解决时间：2026-04-26</v>
+        <v>预计需要2个开发工作日完成修复，包含测试和回归验证。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Y-BUG-077</v>
+        <v>Y-BUG-034</v>
       </c>
       <c r="B38" t="str">
-        <v>文档缺失</v>
+        <v>首页加载性能问题严重，首屏渲染时间超过5秒，需要优化图片压缩、开启懒加载和代码分割</v>
       </c>
       <c r="C38" t="str">
-        <v>周九</v>
+        <v>陈七</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E38" t="str">
-        <v>一般</v>
+        <v>提示</v>
       </c>
       <c r="F38" t="str">
-        <v>根因：界面样式错乱，预计解决时间：2026-04-26</v>
+        <v>【pending】需要与产品确认需求细节，当前需求描述不够清晰。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-09</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Y-BUG-009</v>
+        <v>Y-BUG-049</v>
       </c>
       <c r="B39" t="str">
-        <v>API接口错误</v>
+        <v>用户密码重置功能存在安全漏洞，重置链接未设置过期时间，可能被恶意利用，需要添加token有效期验证</v>
       </c>
       <c r="C39" t="str">
-        <v>吴十</v>
+        <v>赵六</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E39" t="str">
         <v>提示</v>
       </c>
       <c r="F39" t="str">
-        <v/>
+        <v>需要与产品确认需求细节，当前需求描述不够清晰</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Y-BUG-061</v>
+        <v>Y-BUG-042</v>
       </c>
       <c r="B40" t="str">
-        <v>数据加载失败</v>
+        <v>Redis缓存失效导致频繁查询数据库，需要检查缓存更新策略和过期时间设置</v>
       </c>
       <c r="C40" t="str">
-        <v>陈七</v>
+        <v>林四</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-22</v>
       </c>
       <c r="E40" t="str">
-        <v>严重</v>
+        <v>一般</v>
       </c>
       <c r="F40" t="str">
-        <v>根因：支付功能异常，预计解决时间：2026-04-26</v>
+        <v>【deferred】代码review已通过，等待合并到主分支。预计需要2个开发工作日完成修复，包含测试和回归验证。预计解决时间：2026-05-09</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Y-BUG-094</v>
+        <v>Y-BUG-018</v>
       </c>
       <c r="B41" t="str">
-        <v>登录页面崩溃</v>
+        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
       </c>
       <c r="C41" t="str">
-        <v>吴十</v>
+        <v>王二</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E41" t="str">
-        <v>提示</v>
+        <v>严重</v>
       </c>
       <c r="F41" t="str">
-        <v/>
+        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Y-BUG-067</v>
+        <v>Y-BUG-028</v>
       </c>
       <c r="B42" t="str">
-        <v>功能模块缺失</v>
+        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
       </c>
       <c r="C42" t="str">
-        <v>陈三</v>
+        <v>吴十</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-15</v>
+        <v>2026-05-01</v>
       </c>
       <c r="E42" t="str">
         <v>提示</v>
       </c>
       <c r="F42" t="str">
-        <v/>
+        <v>需要与产品确认需求细节，当前需求描述不够清晰</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Y-BUG-096</v>
+        <v>Y-BUG-001</v>
       </c>
       <c r="B43" t="str">
-        <v>缓存失效</v>
+        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
       </c>
       <c r="C43" t="str">
-        <v>吴十</v>
+        <v>陈三</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E43" t="str">
-        <v>一般</v>
+        <v>致命</v>
       </c>
       <c r="F43" t="str">
-        <v>根因：登录页面崩溃，预计解决时间：2026-04-26</v>
+        <v>【长期跟踪】已修复并发布到测试环境，等待测试验证。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Y-BUG-059</v>
+        <v>Y-BUG-013</v>
       </c>
       <c r="B44" t="str">
-        <v>登录页面崩溃</v>
+        <v>支付功能在移动端提交订单时出现网络超时错误，经排查发现是API请求超时时间设置过短，需要调整axios的timeout配置</v>
       </c>
       <c r="C44" t="str">
-        <v>黄五</v>
+        <v>王五</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-29</v>
       </c>
       <c r="E44" t="str">
-        <v>致命</v>
+        <v>提示</v>
       </c>
       <c r="F44" t="str">
-        <v>根因：安全漏洞，预计解决时间：2026-04-26</v>
+        <v>【pending】该问题已在测试环境复现，正在编写修复方案。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Y-BUG-024</v>
+        <v>Y-BUG-041</v>
       </c>
       <c r="B45" t="str">
-        <v>数据库连接失败</v>
+        <v>数据库连接池在高并发场景下出现连接耗尽，需要增加连接池最大连接数配置和连接回收机制</v>
       </c>
       <c r="C45" t="str">
-        <v>黄五</v>
+        <v>吴十</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-22</v>
       </c>
       <c r="E45" t="str">
-        <v>提示</v>
+        <v>严重</v>
       </c>
       <c r="F45" t="str">
-        <v>[deferred] 根因：逻辑错误，预计解决时间：2026-04-26</v>
+        <v>该问题是已知问题，已列入后续迭代计划</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Y-BUG-084</v>
+        <v>Y-BUG-023</v>
       </c>
       <c r="B46" t="str">
-        <v>部署失败</v>
+        <v>首页数据加载失败，显示空白页面，经检查是接口返回数据格式变更导致JSON解析错误，需要更新数据解析逻辑</v>
       </c>
       <c r="C46" t="str">
-        <v>王二</v>
+        <v>郑一</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E46" t="str">
-        <v>严重</v>
+        <v>提示</v>
       </c>
       <c r="F46" t="str">
-        <v/>
+        <v>需要与产品确认需求细节，当前需求描述不够清晰</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Y-BUG-013</v>
+        <v>Y-BUG-056</v>
       </c>
       <c r="B47" t="str">
-        <v>异常处理缺失</v>
+        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
       </c>
       <c r="C47" t="str">
-        <v>李四</v>
+        <v>钱七</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E47" t="str">
-        <v>一般</v>
+        <v>致命</v>
       </c>
       <c r="F47" t="str">
-        <v>[deferred] 根因：部署失败，预计解决时间：2026-04-26</v>
+        <v>代码review已通过，等待合并到主分支</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Y-BUG-088</v>
+        <v>Y-BUG-079</v>
       </c>
       <c r="B48" t="str">
-        <v>支付功能异常</v>
+        <v>首页数据加载失败，显示空白页面，经检查是接口返回数据格式变更导致JSON解析错误，需要更新数据解析逻辑</v>
       </c>
       <c r="C48" t="str">
-        <v>李四</v>
+        <v>林四</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E48" t="str">
-        <v>致命</v>
+        <v>一般</v>
       </c>
       <c r="F48" t="str">
-        <v/>
+        <v>经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。代码review已通过，等待合并到主分支。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Y-BUG-090</v>
+        <v>Y-BUG-061</v>
       </c>
       <c r="B49" t="str">
-        <v>权限问题</v>
+        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
       </c>
       <c r="C49" t="str">
-        <v>周九</v>
+        <v>李四</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E49" t="str">
-        <v>致命</v>
+        <v>一般</v>
       </c>
       <c r="F49" t="str">
-        <v>[长期跟踪] 根因：登录页面崩溃，预计解决时间：2026-04-26</v>
+        <v>该问题是已知问题，已列入后续迭代计划</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Y-BUG-065</v>
+        <v>Y-BUG-024</v>
       </c>
       <c r="B50" t="str">
-        <v>性能问题</v>
+        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
       </c>
       <c r="C50" t="str">
-        <v>李四</v>
+        <v>周九</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E50" t="str">
-        <v>致命</v>
+        <v>一般</v>
       </c>
       <c r="F50" t="str">
-        <v>[暂不处理] 根因：兼容性问题，预计解决时间：2026-04-26</v>
+        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Y-BUG-027</v>
+        <v>Y-BUG-083</v>
       </c>
       <c r="B51" t="str">
-        <v>缓存失效</v>
+        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
       </c>
       <c r="C51" t="str">
-        <v>孙八</v>
+        <v>张三</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-22</v>
       </c>
       <c r="E51" t="str">
-        <v>一般</v>
+        <v>致命</v>
       </c>
       <c r="F51" t="str">
-        <v>根因：测试用例不足，预计解决时间：2026-04-26</v>
+        <v>【暂不处理】该问题已在测试环境复现，正在编写修复方案。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Y-BUG-053</v>
+        <v>Y-BUG-086</v>
       </c>
       <c r="B52" t="str">
-        <v>数据库连接失败</v>
+        <v>配置文件管理混乱，开发环境和生产环境配置混用，需要建立统一的配置管理方案</v>
       </c>
       <c r="C52" t="str">
-        <v>钱七</v>
+        <v>陈三</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E52" t="str">
-        <v>严重</v>
+        <v>致命</v>
       </c>
       <c r="F52" t="str">
-        <v>[deferred] 根因：配置错误，预计解决时间：2026-04-26</v>
+        <v>经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Y-BUG-089</v>
+        <v>Y-BUG-054</v>
       </c>
       <c r="B53" t="str">
-        <v>用户体验优化</v>
+        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
       </c>
       <c r="C53" t="str">
-        <v>张三</v>
+        <v>王二</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E53" t="str">
-        <v>致命</v>
+        <v>严重</v>
       </c>
       <c r="F53" t="str">
-        <v/>
+        <v>已修复并发布到测试环境，等待测试验证</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Y-BUG-005</v>
+        <v>Y-BUG-053</v>
       </c>
       <c r="B54" t="str">
-        <v>功能模块缺失</v>
+        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
       </c>
       <c r="C54" t="str">
-        <v>孙八</v>
+        <v>刘六</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-23</v>
+        <v>2026-05-01</v>
       </c>
       <c r="E54" t="str">
         <v>严重</v>
       </c>
       <c r="F54" t="str">
-        <v/>
+        <v>该问题是已知问题，已列入后续迭代计划。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Y-BUG-017</v>
+        <v>Y-BUG-072</v>
       </c>
       <c r="B55" t="str">
-        <v>支付功能异常</v>
+        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
       </c>
       <c r="C55" t="str">
-        <v>李四</v>
+        <v>钱七</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E55" t="str">
-        <v>一般</v>
+        <v>致命</v>
       </c>
       <c r="F55" t="str">
-        <v>根因：逻辑错误，预计解决时间：2026-04-26</v>
+        <v>需要与产品确认需求细节，当前需求描述不够清晰。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Y-BUG-092</v>
+        <v>Y-BUG-036</v>
       </c>
       <c r="B56" t="str">
-        <v>数据库连接失败</v>
+        <v>用户注册API接口返回400错误，参数验证失败，需要检查请求参数格式和后端验证逻辑是否匹配</v>
       </c>
       <c r="C56" t="str">
-        <v>张三</v>
+        <v>吴十</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-22</v>
       </c>
       <c r="E56" t="str">
-        <v>提示</v>
+        <v>严重</v>
       </c>
       <c r="F56" t="str">
-        <v>根因：API接口错误，预计解决时间：2026-04-26</v>
+        <v>【跟踪中】已经定位到问题根因，是由于异步请求时序问题导致状态不一致。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-07</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Y-BUG-035</v>
+        <v>Y-BUG-066</v>
       </c>
       <c r="B57" t="str">
-        <v>缓存失效</v>
+        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
       </c>
       <c r="C57" t="str">
-        <v>刘六</v>
+        <v>周九</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-29</v>
       </c>
       <c r="E57" t="str">
-        <v>严重</v>
+        <v>提示</v>
       </c>
       <c r="F57" t="str">
-        <v>[长期跟踪] 根因：性能问题，预计解决时间：2026-04-26</v>
+        <v>【长期跟踪】需要升级依赖库版本，但可能影响其他模块，需要评估风险。需要升级依赖库版本，但可能影响其他模块，需要评估风险。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Y-BUG-015</v>
+        <v>Y-BUG-033</v>
       </c>
       <c r="B58" t="str">
-        <v>权限问题</v>
+        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
       </c>
       <c r="C58" t="str">
-        <v>王五</v>
+        <v>刘六</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E58" t="str">
-        <v>提示</v>
+        <v>一般</v>
       </c>
       <c r="F58" t="str">
-        <v>根因：安全漏洞，预计解决时间：2026-04-26</v>
+        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Y-BUG-032</v>
+        <v>Y-BUG-060</v>
       </c>
       <c r="B59" t="str">
-        <v>数据库连接失败</v>
+        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
       </c>
       <c r="C59" t="str">
-        <v>王二</v>
+        <v>赵六</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-25</v>
       </c>
       <c r="E59" t="str">
-        <v>严重</v>
+        <v>提示</v>
       </c>
       <c r="F59" t="str">
-        <v/>
+        <v>该问题已在测试环境复现，正在编写修复方案</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Y-BUG-074</v>
+        <v>Y-BUG-081</v>
       </c>
       <c r="B60" t="str">
-        <v>兼容性问题</v>
+        <v>用户列表页面在小屏幕设备上样式错乱，表格列重叠，需要优化响应式布局和媒体查询设置</v>
       </c>
       <c r="C60" t="str">
-        <v>陈三</v>
+        <v>王五</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E60" t="str">
-        <v>致命</v>
+        <v>一般</v>
       </c>
       <c r="F60" t="str">
-        <v>根因：代码冗余，预计解决时间：2026-04-26</v>
+        <v>【deferred】涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Y-BUG-073</v>
+        <v>Y-BUG-047</v>
       </c>
       <c r="B61" t="str">
-        <v>代码冗余</v>
+        <v>数据库连接池在高并发场景下出现连接耗尽，需要增加连接池最大连接数配置和连接回收机制</v>
       </c>
       <c r="C61" t="str">
-        <v>周九</v>
+        <v>孙八</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E61" t="str">
-        <v>一般</v>
+        <v>提示</v>
       </c>
       <c r="F61" t="str">
-        <v>根因：异常处理缺失，预计解决时间：2026-04-26</v>
+        <v>【deferred】代码review已通过，等待合并到主分支。代码review已通过，等待合并到主分支。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Y-BUG-002</v>
+        <v>Y-BUG-087</v>
       </c>
       <c r="B62" t="str">
-        <v>权限问题</v>
+        <v>首页数据加载失败，显示空白页面，经检查是接口返回数据格式变更导致JSON解析错误，需要更新数据解析逻辑</v>
       </c>
       <c r="C62" t="str">
         <v>王五</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-22</v>
       </c>
       <c r="E62" t="str">
-        <v>严重</v>
+        <v>致命</v>
       </c>
       <c r="F62" t="str">
-        <v>根因：测试用例不足，预计解决时间：2026-04-26</v>
+        <v>【暂不处理】经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Y-BUG-049</v>
+        <v>Y-BUG-092</v>
       </c>
       <c r="B63" t="str">
-        <v>性能问题</v>
+        <v>用户列表页面在小屏幕设备上样式错乱，表格列重叠，需要优化响应式布局和媒体查询设置</v>
       </c>
       <c r="C63" t="str">
-        <v>刘六</v>
+        <v>郑一</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E63" t="str">
-        <v>一般</v>
+        <v>致命</v>
       </c>
       <c r="F63" t="str">
-        <v>[pending] 根因：性能问题，预计解决时间：2026-04-26</v>
+        <v>该问题是已知问题，已列入后续迭代计划</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Y-BUG-063</v>
+        <v>Y-BUG-065</v>
       </c>
       <c r="B64" t="str">
-        <v>逻辑错误</v>
+        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
       </c>
       <c r="C64" t="str">
         <v>黄五</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E64" t="str">
         <v>提示</v>
       </c>
       <c r="F64" t="str">
-        <v>根因：功能模块缺失，预计解决时间：2026-04-26</v>
+        <v>【跟踪中】预计需要2个开发工作日完成修复，包含测试和回归验证。代码review已通过，等待合并到主分支。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Y-BUG-046</v>
+        <v>Y-BUG-097</v>
       </c>
       <c r="B65" t="str">
-        <v>权限问题</v>
+        <v>Redis缓存失效导致频繁查询数据库，需要检查缓存更新策略和过期时间设置</v>
       </c>
       <c r="C65" t="str">
         <v>杨八</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E65" t="str">
-        <v>严重</v>
+        <v>致命</v>
       </c>
       <c r="F65" t="str">
-        <v>[长期跟踪] 根因：用户体验优化，预计解决时间：2026-04-26</v>
+        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Y-BUG-006</v>
+        <v>Y-BUG-099</v>
       </c>
       <c r="B66" t="str">
-        <v>代码冗余</v>
+        <v>CI/CD部署失败，Docker镜像构建超时，需要优化构建脚本和依赖下载速度</v>
       </c>
       <c r="C66" t="str">
-        <v>黄五</v>
+        <v>林四</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E66" t="str">
-        <v>致命</v>
+        <v>提示</v>
       </c>
       <c r="F66" t="str">
-        <v>[暂不处理] 根因：兼容性问题，预计解决时间：2026-04-26</v>
+        <v>【跟踪中】该问题是已知问题，已列入后续迭代计划。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-08</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Y-BUG-030</v>
+        <v>Y-BUG-057</v>
       </c>
       <c r="B67" t="str">
-        <v>数据加载失败</v>
+        <v>用户密码重置功能存在安全漏洞，重置链接未设置过期时间，可能被恶意利用，需要添加token有效期验证</v>
       </c>
       <c r="C67" t="str">
-        <v>孙八</v>
+        <v>李四</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-29</v>
       </c>
       <c r="E67" t="str">
-        <v>严重</v>
+        <v>致命</v>
       </c>
       <c r="F67" t="str">
-        <v>根因：缓存失效，预计解决时间：2026-04-26</v>
+        <v>代码review已通过，等待合并到主分支。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Y-BUG-001</v>
+        <v>Y-BUG-088</v>
       </c>
       <c r="B68" t="str">
-        <v>数据加载失败</v>
+        <v>数据库连接池在高并发场景下出现连接耗尽，需要增加连接池最大连接数配置和连接回收机制</v>
       </c>
       <c r="C68" t="str">
-        <v>李四</v>
+        <v>黄五</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E68" t="str">
-        <v>提示</v>
+        <v>一般</v>
       </c>
       <c r="F68" t="str">
-        <v/>
+        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Y-BUG-039</v>
+        <v>Y-BUG-095</v>
       </c>
       <c r="B69" t="str">
-        <v>兼容性问题</v>
+        <v>用户注册API接口返回400错误，参数验证失败，需要检查请求参数格式和后端验证逻辑是否匹配</v>
       </c>
       <c r="C69" t="str">
         <v>钱七</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-22</v>
       </c>
       <c r="E69" t="str">
-        <v>致命</v>
+        <v>一般</v>
       </c>
       <c r="F69" t="str">
-        <v/>
+        <v>【暂不处理】代码review已通过，等待合并到主分支。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Y-BUG-041</v>
+        <v>Y-BUG-052</v>
       </c>
       <c r="B70" t="str">
-        <v>代码冗余</v>
+        <v>CI/CD部署失败，Docker镜像构建超时，需要优化构建脚本和依赖下载速度</v>
       </c>
       <c r="C70" t="str">
-        <v>赵六</v>
+        <v>王二</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E70" t="str">
-        <v>提示</v>
+        <v>致命</v>
       </c>
       <c r="F70" t="str">
-        <v>根因：界面样式错乱，预计解决时间：2026-04-26</v>
+        <v>【长期跟踪】该问题是已知问题，已列入后续迭代计划。代码review已通过，等待合并到主分支。预计解决时间：2026-05-09</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Y-BUG-087</v>
+        <v>Y-BUG-074</v>
       </c>
       <c r="B71" t="str">
-        <v>异常处理缺失</v>
+        <v>iOS端App在iOS 15以下版本兼容性问题，某些功能按钮点击无响应，需要检查事件绑定方式</v>
       </c>
       <c r="C71" t="str">
-        <v>吴十</v>
+        <v>陈三</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-24</v>
@@ -1816,207 +1816,207 @@
         <v>一般</v>
       </c>
       <c r="F71" t="str">
-        <v>[跟踪中] 根因：支付功能异常，预计解决时间：2026-04-26</v>
+        <v>该问题已在测试环境复现，正在编写修复方案。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Y-BUG-055</v>
+        <v>Y-BUG-089</v>
       </c>
       <c r="B72" t="str">
-        <v>测试用例不足</v>
+        <v>iOS端App在iOS 15以下版本兼容性问题，某些功能按钮点击无响应，需要检查事件绑定方式</v>
       </c>
       <c r="C72" t="str">
-        <v>吴十</v>
+        <v>孙八</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-29</v>
       </c>
       <c r="E72" t="str">
-        <v>致命</v>
+        <v>严重</v>
       </c>
       <c r="F72" t="str">
-        <v/>
+        <v>该问题已在测试环境复现，正在编写修复方案。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Y-BUG-069</v>
+        <v>Y-BUG-093</v>
       </c>
       <c r="B73" t="str">
-        <v>测试用例不足</v>
+        <v>用户注册API接口返回400错误，参数验证失败，需要检查请求参数格式和后端验证逻辑是否匹配</v>
       </c>
       <c r="C73" t="str">
-        <v>吴十</v>
+        <v>陈三</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E73" t="str">
-        <v>一般</v>
+        <v>严重</v>
       </c>
       <c r="F73" t="str">
-        <v>[跟踪中] 根因：用户体验优化，预计解决时间：2026-04-26</v>
+        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Y-BUG-070</v>
+        <v>Y-BUG-064</v>
       </c>
       <c r="B74" t="str">
-        <v>API接口错误</v>
+        <v>代码冗余严重，多个组件存在重复逻辑，需要抽取公共组件和工具函数，提高代码复用率</v>
       </c>
       <c r="C74" t="str">
-        <v>周九</v>
+        <v>王五</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E74" t="str">
-        <v>一般</v>
+        <v>严重</v>
       </c>
       <c r="F74" t="str">
-        <v/>
+        <v>代码review已通过，等待合并到主分支</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Y-BUG-083</v>
+        <v>Y-BUG-100</v>
       </c>
       <c r="B75" t="str">
-        <v>性能问题</v>
+        <v>订单状态流转逻辑错误，已取消的订单仍能继续支付，需要修复状态机转换规则</v>
       </c>
       <c r="C75" t="str">
         <v>郑一</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E75" t="str">
-        <v>一般</v>
+        <v>严重</v>
       </c>
       <c r="F75" t="str">
-        <v/>
+        <v>该问题是已知问题，已列入后续迭代计划</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Y-BUG-091</v>
+        <v>Y-BUG-076</v>
       </c>
       <c r="B76" t="str">
-        <v>API接口错误</v>
+        <v>用户权限验证逻辑存在漏洞，普通用户可以访问管理员页面，需要加强路由守卫和权限检查</v>
       </c>
       <c r="C76" t="str">
-        <v>黄五</v>
+        <v>陈七</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-29</v>
       </c>
       <c r="E76" t="str">
-        <v>提示</v>
+        <v>严重</v>
       </c>
       <c r="F76" t="str">
-        <v/>
+        <v>该问题是已知问题，已列入后续迭代计划。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Y-BUG-037</v>
+        <v>Y-BUG-080</v>
       </c>
       <c r="B77" t="str">
-        <v>安全漏洞</v>
+        <v>用户权限验证逻辑存在漏洞，普通用户可以访问管理员页面，需要加强路由守卫和权限检查</v>
       </c>
       <c r="C77" t="str">
-        <v>郑一</v>
+        <v>刘六</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-19</v>
+        <v>2026-05-01</v>
       </c>
       <c r="E77" t="str">
-        <v>提示</v>
+        <v>一般</v>
       </c>
       <c r="F77" t="str">
-        <v>根因：性能问题，预计解决时间：2026-04-26</v>
+        <v>经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Y-BUG-095</v>
+        <v>Y-BUG-051</v>
       </c>
       <c r="B78" t="str">
-        <v>界面样式错乱</v>
+        <v>代码冗余严重，多个组件存在重复逻辑，需要抽取公共组件和工具函数，提高代码复用率</v>
       </c>
       <c r="C78" t="str">
-        <v>陈七</v>
+        <v>黄五</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E78" t="str">
-        <v>提示</v>
+        <v>严重</v>
       </c>
       <c r="F78" t="str">
-        <v>根因：兼容性问题，预计解决时间：2026-04-26</v>
+        <v>代码review已通过，等待合并到主分支。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Y-BUG-098</v>
+        <v>Y-BUG-096</v>
       </c>
       <c r="B79" t="str">
-        <v>权限问题</v>
+        <v>用户列表页面在小屏幕设备上样式错乱，表格列重叠，需要优化响应式布局和媒体查询设置</v>
       </c>
       <c r="C79" t="str">
-        <v>周九</v>
+        <v>王二</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-19</v>
+        <v>2026-05-01</v>
       </c>
       <c r="E79" t="str">
-        <v>严重</v>
+        <v>致命</v>
       </c>
       <c r="F79" t="str">
-        <v/>
+        <v>【pending】预计需要2个开发工作日完成修复，包含测试和回归验证。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Y-BUG-021</v>
+        <v>Y-BUG-055</v>
       </c>
       <c r="B80" t="str">
-        <v>数据加载失败</v>
+        <v>测试用例覆盖率不足60%，核心功能缺少单元测试，需要补充测试用例确保代码质量</v>
       </c>
       <c r="C80" t="str">
-        <v>赵六</v>
+        <v>黄五</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E80" t="str">
-        <v>严重</v>
+        <v>提示</v>
       </c>
       <c r="F80" t="str">
-        <v/>
+        <v>该问题是已知问题，已列入后续迭代计划</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Y-BUG-031</v>
+        <v>Y-BUG-062</v>
       </c>
       <c r="B81" t="str">
-        <v>功能模块缺失</v>
+        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
       </c>
       <c r="C81" t="str">
-        <v>王二</v>
+        <v>杨八</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-22</v>
       </c>
       <c r="E81" t="str">
         <v>严重</v>
       </c>
       <c r="F81" t="str">
-        <v>[跟踪中] 根因：用户体验优化，预计解决时间：2026-04-26</v>
+        <v>【跟踪中】已修复并发布到测试环境，等待测试验证。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="82">
@@ -2024,19 +2024,19 @@
         <v>T-BUG-001</v>
       </c>
       <c r="B82" t="str">
-        <v>异常处理缺失</v>
+        <v>数据库连接池在高并发场景下出现连接耗尽，需要增加连接池最大连接数配置和连接回收机制</v>
       </c>
       <c r="C82" t="str">
-        <v>吴十</v>
+        <v>张三</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E82" t="str">
         <v>严重</v>
       </c>
       <c r="F82" t="str">
-        <v>[暂不处理] 根因：代码冗余，预计解决时间：2026-04-26</v>
+        <v>该问题是已知问题，已列入后续迭代计划</v>
       </c>
     </row>
     <row r="83">
@@ -2044,19 +2044,19 @@
         <v>T-BUG-002</v>
       </c>
       <c r="B83" t="str">
-        <v>文档缺失</v>
+        <v>首页加载性能问题严重，首屏渲染时间超过5秒，需要优化图片压缩、开启懒加载和代码分割</v>
       </c>
       <c r="C83" t="str">
-        <v>赵六</v>
+        <v>林四</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E83" t="str">
-        <v>严重</v>
+        <v>致命</v>
       </c>
       <c r="F83" t="str">
-        <v/>
+        <v>【长期跟踪】预计需要2个开发工作日完成修复，包含测试和回归验证。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-07</v>
       </c>
     </row>
     <row r="84">
@@ -2064,19 +2064,19 @@
         <v>T-BUG-003</v>
       </c>
       <c r="B84" t="str">
-        <v>权限问题</v>
+        <v>用户反馈弹窗关闭按钮位置不合理，用户容易误触，需要优化UI布局和交互体验</v>
       </c>
       <c r="C84" t="str">
-        <v>林四</v>
+        <v>陈七</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-29</v>
       </c>
       <c r="E84" t="str">
-        <v>严重</v>
+        <v>一般</v>
       </c>
       <c r="F84" t="str">
-        <v/>
+        <v>该问题已在测试环境复现，正在编写修复方案</v>
       </c>
     </row>
     <row r="85">
@@ -2084,19 +2084,19 @@
         <v>T-BUG-004</v>
       </c>
       <c r="B85" t="str">
-        <v>配置错误</v>
+        <v>代码冗余严重，多个组件存在重复逻辑，需要抽取公共组件和工具函数，提高代码复用率</v>
       </c>
       <c r="C85" t="str">
-        <v>刘六</v>
+        <v>钱七</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-24</v>
+        <v>2026-05-01</v>
       </c>
       <c r="E85" t="str">
-        <v>严重</v>
+        <v>提示</v>
       </c>
       <c r="F85" t="str">
-        <v/>
+        <v>需要与产品确认需求细节，当前需求描述不够清晰</v>
       </c>
     </row>
     <row r="86">
@@ -2104,19 +2104,19 @@
         <v>T-BUG-005</v>
       </c>
       <c r="B86" t="str">
-        <v>配置错误</v>
+        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
       </c>
       <c r="C86" t="str">
-        <v>郑一</v>
+        <v>王五</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-20</v>
+        <v>2026-05-01</v>
       </c>
       <c r="E86" t="str">
-        <v>一般</v>
+        <v>提示</v>
       </c>
       <c r="F86" t="str">
-        <v>根因：支付功能异常，预计解决时间：2026-04-26</v>
+        <v>预计需要2个开发工作日完成修复，包含测试和回归验证。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="87">
@@ -2124,19 +2124,19 @@
         <v>T-BUG-006</v>
       </c>
       <c r="B87" t="str">
-        <v>界面样式错乱</v>
+        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
       </c>
       <c r="C87" t="str">
-        <v>黄五</v>
+        <v>张三</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E87" t="str">
         <v>一般</v>
       </c>
       <c r="F87" t="str">
-        <v/>
+        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="88">
@@ -2144,19 +2144,19 @@
         <v>T-BUG-007</v>
       </c>
       <c r="B88" t="str">
-        <v>数据加载失败</v>
+        <v>支付功能在移动端提交订单时出现网络超时错误，经排查发现是API请求超时时间设置过短，需要调整axios的timeout配置</v>
       </c>
       <c r="C88" t="str">
-        <v>陈七</v>
+        <v>张三</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E88" t="str">
         <v>严重</v>
       </c>
       <c r="F88" t="str">
-        <v>根因：异常处理缺失，预计解决时间：2026-04-26</v>
+        <v>已修复并发布到测试环境，等待测试验证。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="89">
@@ -2164,19 +2164,19 @@
         <v>T-BUG-008</v>
       </c>
       <c r="B89" t="str">
-        <v>缓存失效</v>
+        <v>iOS端App在iOS 15以下版本兼容性问题，某些功能按钮点击无响应，需要检查事件绑定方式</v>
       </c>
       <c r="C89" t="str">
-        <v>李四</v>
+        <v>陈七</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-26</v>
       </c>
       <c r="E89" t="str">
-        <v>提示</v>
+        <v>致命</v>
       </c>
       <c r="F89" t="str">
-        <v>[deferred] 根因：权限问题，预计解决时间：2026-04-26</v>
+        <v>已修复并发布到测试环境，等待测试验证。代码review已通过，等待合并到主分支。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="90">
@@ -2184,19 +2184,19 @@
         <v>T-BUG-009</v>
       </c>
       <c r="B90" t="str">
-        <v>测试用例不足</v>
+        <v>配置文件管理混乱，开发环境和生产环境配置混用，需要建立统一的配置管理方案</v>
       </c>
       <c r="C90" t="str">
-        <v>王二</v>
+        <v>孙八</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E90" t="str">
-        <v>严重</v>
+        <v>一般</v>
       </c>
       <c r="F90" t="str">
-        <v>[跟踪中] 根因：支付功能异常，预计解决时间：2026-04-26</v>
+        <v>该问题是已知问题，已列入后续迭代计划。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="91">
@@ -2204,19 +2204,19 @@
         <v>T-BUG-010</v>
       </c>
       <c r="B91" t="str">
-        <v>缓存失效</v>
+        <v>首页加载性能问题严重，首屏渲染时间超过5秒，需要优化图片压缩、开启懒加载和代码分割</v>
       </c>
       <c r="C91" t="str">
-        <v>王二</v>
+        <v>张三</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E91" t="str">
-        <v>一般</v>
+        <v>提示</v>
       </c>
       <c r="F91" t="str">
-        <v>根因：配置错误，预计解决时间：2026-04-26</v>
+        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持</v>
       </c>
     </row>
     <row r="92">
@@ -2224,19 +2224,19 @@
         <v>T-BUG-011</v>
       </c>
       <c r="B92" t="str">
-        <v>缓存失效</v>
+        <v>支付功能在移动端提交订单时出现网络超时错误，经排查发现是API请求超时时间设置过短，需要调整axios的timeout配置</v>
       </c>
       <c r="C92" t="str">
-        <v>黄五</v>
+        <v>张三</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E92" t="str">
         <v>严重</v>
       </c>
       <c r="F92" t="str">
-        <v>根因：逻辑错误，预计解决时间：2026-04-26</v>
+        <v>经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查</v>
       </c>
     </row>
     <row r="93">
@@ -2244,19 +2244,19 @@
         <v>T-BUG-012</v>
       </c>
       <c r="B93" t="str">
-        <v>界面样式错乱</v>
+        <v>测试用例覆盖率不足60%，核心功能缺少单元测试，需要补充测试用例确保代码质量</v>
       </c>
       <c r="C93" t="str">
-        <v>杨八</v>
+        <v>陈七</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-22</v>
       </c>
       <c r="E93" t="str">
-        <v>一般</v>
+        <v>提示</v>
       </c>
       <c r="F93" t="str">
-        <v/>
+        <v>代码review已通过，等待合并到主分支。代码review已通过，等待合并到主分支。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="94">
@@ -2264,19 +2264,19 @@
         <v>T-BUG-013</v>
       </c>
       <c r="B94" t="str">
-        <v>安全漏洞</v>
+        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
       </c>
       <c r="C94" t="str">
-        <v>林四</v>
+        <v>周九</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-29</v>
       </c>
       <c r="E94" t="str">
-        <v>提示</v>
+        <v>一般</v>
       </c>
       <c r="F94" t="str">
-        <v/>
+        <v>【暂不处理】已修复并发布到测试环境，等待测试验证。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="95">
@@ -2284,19 +2284,19 @@
         <v>T-BUG-014</v>
       </c>
       <c r="B95" t="str">
-        <v>界面样式错乱</v>
+        <v>配置文件管理混乱，开发环境和生产环境配置混用，需要建立统一的配置管理方案</v>
       </c>
       <c r="C95" t="str">
         <v>张三</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E95" t="str">
-        <v>提示</v>
+        <v>致命</v>
       </c>
       <c r="F95" t="str">
-        <v>[长期跟踪] 根因：功能模块缺失，预计解决时间：2026-04-26</v>
+        <v>已修复并发布到测试环境，等待测试验证</v>
       </c>
     </row>
     <row r="96">
@@ -2304,19 +2304,19 @@
         <v>T-BUG-015</v>
       </c>
       <c r="B96" t="str">
-        <v>逻辑错误</v>
+        <v>测试用例覆盖率不足60%，核心功能缺少单元测试，需要补充测试用例确保代码质量</v>
       </c>
       <c r="C96" t="str">
-        <v>张三</v>
+        <v>陈三</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E96" t="str">
-        <v>提示</v>
+        <v>致命</v>
       </c>
       <c r="F96" t="str">
-        <v>根因：兼容性问题，预计解决时间：2026-04-26</v>
+        <v>预计需要2个开发工作日完成修复，包含测试和回归验证。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="97">
@@ -2324,19 +2324,19 @@
         <v>T-BUG-016</v>
       </c>
       <c r="B97" t="str">
-        <v>缓存失效</v>
+        <v>用户权限验证逻辑存在漏洞，普通用户可以访问管理员页面，需要加强路由守卫和权限检查</v>
       </c>
       <c r="C97" t="str">
-        <v>李四</v>
+        <v>张三</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E97" t="str">
         <v>提示</v>
       </c>
       <c r="F97" t="str">
-        <v>根因：异常处理缺失，预计解决时间：2026-04-26</v>
+        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持</v>
       </c>
     </row>
     <row r="98">
@@ -2344,19 +2344,19 @@
         <v>T-BUG-017</v>
       </c>
       <c r="B98" t="str">
-        <v>缓存失效</v>
+        <v>订单状态流转逻辑错误，已取消的订单仍能继续支付，需要修复状态机转换规则</v>
       </c>
       <c r="C98" t="str">
-        <v>钱七</v>
+        <v>孙八</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E98" t="str">
-        <v>严重</v>
+        <v>致命</v>
       </c>
       <c r="F98" t="str">
-        <v>根因：逻辑错误，预计解决时间：2026-04-26</v>
+        <v>该问题已在测试环境复现，正在编写修复方案。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="99">
@@ -2364,19 +2364,19 @@
         <v>T-BUG-018</v>
       </c>
       <c r="B99" t="str">
-        <v>用户体验优化</v>
+        <v>支付功能在移动端提交订单时出现网络超时错误，经排查发现是API请求超时时间设置过短，需要调整axios的timeout配置</v>
       </c>
       <c r="C99" t="str">
-        <v>张三</v>
+        <v>王二</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-25</v>
       </c>
       <c r="E99" t="str">
-        <v>一般</v>
+        <v>致命</v>
       </c>
       <c r="F99" t="str">
-        <v>[长期跟踪] 根因：逻辑错误，预计解决时间：2026-04-26</v>
+        <v>已修复并发布到测试环境，等待测试验证</v>
       </c>
     </row>
     <row r="100">
@@ -2384,19 +2384,19 @@
         <v>T-BUG-019</v>
       </c>
       <c r="B100" t="str">
-        <v>代码冗余</v>
+        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
       </c>
       <c r="C100" t="str">
-        <v>李四</v>
+        <v>杨八</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-25</v>
       </c>
       <c r="E100" t="str">
-        <v>严重</v>
+        <v>提示</v>
       </c>
       <c r="F100" t="str">
-        <v>根因：兼容性问题，预计解决时间：2026-04-26</v>
+        <v>【暂不处理】预计需要2个开发工作日完成修复，包含测试和回归验证。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-09</v>
       </c>
     </row>
     <row r="101">
@@ -2404,19 +2404,19 @@
         <v>T-BUG-020</v>
       </c>
       <c r="B101" t="str">
-        <v>异常处理缺失</v>
+        <v>首页数据加载失败，显示空白页面，经检查是接口返回数据格式变更导致JSON解析错误，需要更新数据解析逻辑</v>
       </c>
       <c r="C101" t="str">
-        <v>陈七</v>
+        <v>吴十</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E101" t="str">
-        <v>严重</v>
+        <v>提示</v>
       </c>
       <c r="F101" t="str">
-        <v>根因：权限问题，预计解决时间：2026-04-26</v>
+        <v>【deferred】经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-09</v>
       </c>
     </row>
     <row r="102">
@@ -2424,19 +2424,19 @@
         <v>T-BUG-021</v>
       </c>
       <c r="B102" t="str">
-        <v>配置错误</v>
+        <v>支付功能在移动端提交订单时出现网络超时错误，经排查发现是API请求超时时间设置过短，需要调整axios的timeout配置</v>
       </c>
       <c r="C102" t="str">
-        <v>郑一</v>
+        <v>王二</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E102" t="str">
         <v>一般</v>
       </c>
       <c r="F102" t="str">
-        <v>[pending] 根因：文档缺失，预计解决时间：2026-04-26</v>
+        <v>经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="103">
@@ -2444,10 +2444,10 @@
         <v>T-BUG-022</v>
       </c>
       <c r="B103" t="str">
-        <v>数据库连接失败</v>
+        <v>数据库连接池在高并发场景下出现连接耗尽，需要增加连接池最大连接数配置和连接回收机制</v>
       </c>
       <c r="C103" t="str">
-        <v>林四</v>
+        <v>刘六</v>
       </c>
       <c r="D103" t="str">
         <v>2026-04-26</v>
@@ -2456,7 +2456,7 @@
         <v>严重</v>
       </c>
       <c r="F103" t="str">
-        <v>[deferred] 根因：API接口错误，预计解决时间：2026-04-26</v>
+        <v>【pending】已经定位到问题根因，是由于异步请求时序问题导致状态不一致。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="104">
@@ -2464,19 +2464,19 @@
         <v>T-BUG-023</v>
       </c>
       <c r="B104" t="str">
-        <v>权限问题</v>
+        <v>支付功能在移动端提交订单时出现网络超时错误，经排查发现是API请求超时时间设置过短，需要调整axios的timeout配置</v>
       </c>
       <c r="C104" t="str">
-        <v>王五</v>
+        <v>张三</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E104" t="str">
-        <v>提示</v>
+        <v>致命</v>
       </c>
       <c r="F104" t="str">
-        <v>[pending] 根因：用户体验优化，预计解决时间：2026-04-26</v>
+        <v>经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查</v>
       </c>
     </row>
     <row r="105">
@@ -2484,19 +2484,19 @@
         <v>T-BUG-024</v>
       </c>
       <c r="B105" t="str">
-        <v>缓存失效</v>
+        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
       </c>
       <c r="C105" t="str">
-        <v>赵六</v>
+        <v>杨八</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E105" t="str">
-        <v>提示</v>
+        <v>一般</v>
       </c>
       <c r="F105" t="str">
-        <v>[暂不处理] 根因：数据加载失败，预计解决时间：2026-04-26</v>
+        <v>【deferred】预计需要2个开发工作日完成修复，包含测试和回归验证。需要升级依赖库版本，但可能影响其他模块，需要评估风险。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="106">
@@ -2504,19 +2504,19 @@
         <v>T-BUG-025</v>
       </c>
       <c r="B106" t="str">
-        <v>数据加载失败</v>
+        <v>用户权限验证逻辑存在漏洞，普通用户可以访问管理员页面，需要加强路由守卫和权限检查</v>
       </c>
       <c r="C106" t="str">
-        <v>王五</v>
+        <v>黄五</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E106" t="str">
-        <v>提示</v>
+        <v>严重</v>
       </c>
       <c r="F106" t="str">
-        <v>[deferred] 根因：代码冗余，预计解决时间：2026-04-26</v>
+        <v>【长期跟踪】预计需要2个开发工作日完成修复，包含测试和回归验证。预计需要2个开发工作日完成修复，包含测试和回归验证。预计解决时间：2026-05-07</v>
       </c>
     </row>
     <row r="107">
@@ -2524,19 +2524,19 @@
         <v>T-BUG-026</v>
       </c>
       <c r="B107" t="str">
-        <v>API接口错误</v>
+        <v>Redis缓存失效导致频繁查询数据库，需要检查缓存更新策略和过期时间设置</v>
       </c>
       <c r="C107" t="str">
-        <v>陈三</v>
+        <v>林四</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E107" t="str">
-        <v>致命</v>
+        <v>严重</v>
       </c>
       <c r="F107" t="str">
-        <v>[暂不处理] 根因：数据加载失败，预计解决时间：2026-04-26</v>
+        <v>代码review已通过，等待合并到主分支</v>
       </c>
     </row>
     <row r="108">
@@ -2544,19 +2544,19 @@
         <v>T-BUG-027</v>
       </c>
       <c r="B108" t="str">
-        <v>测试用例不足</v>
+        <v>用户密码重置功能存在安全漏洞，重置链接未设置过期时间，可能被恶意利用，需要添加token有效期验证</v>
       </c>
       <c r="C108" t="str">
-        <v>李四</v>
+        <v>郑一</v>
       </c>
       <c r="D108" t="str">
         <v>2026-04-25</v>
       </c>
       <c r="E108" t="str">
-        <v>严重</v>
+        <v>一般</v>
       </c>
       <c r="F108" t="str">
-        <v>[pending] 根因：异常处理缺失，预计解决时间：2026-04-26</v>
+        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致。已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="109">
@@ -2564,19 +2564,19 @@
         <v>T-BUG-028</v>
       </c>
       <c r="B109" t="str">
-        <v>逻辑错误</v>
+        <v>iOS端App在iOS 15以下版本兼容性问题，某些功能按钮点击无响应，需要检查事件绑定方式</v>
       </c>
       <c r="C109" t="str">
-        <v>张三</v>
+        <v>杨八</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E109" t="str">
-        <v>致命</v>
+        <v>严重</v>
       </c>
       <c r="F109" t="str">
-        <v>[长期跟踪] 根因：界面样式错乱，预计解决时间：2026-04-26</v>
+        <v>该问题是已知问题，已列入后续迭代计划</v>
       </c>
     </row>
     <row r="110">
@@ -2584,19 +2584,19 @@
         <v>T-BUG-029</v>
       </c>
       <c r="B110" t="str">
-        <v>逻辑错误</v>
+        <v>首页加载性能问题严重，首屏渲染时间超过5秒，需要优化图片压缩、开启懒加载和代码分割</v>
       </c>
       <c r="C110" t="str">
         <v>陈三</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-04-19</v>
+        <v>2026-05-01</v>
       </c>
       <c r="E110" t="str">
-        <v>致命</v>
+        <v>提示</v>
       </c>
       <c r="F110" t="str">
-        <v>根因：登录页面崩溃，预计解决时间：2026-04-26</v>
+        <v>【deferred】该问题已在测试环境复现，正在编写修复方案。需要升级依赖库版本，但可能影响其他模块，需要评估风险。预计解决时间：2026-05-06</v>
       </c>
     </row>
     <row r="111">
@@ -2604,19 +2604,19 @@
         <v>T-BUG-030</v>
       </c>
       <c r="B111" t="str">
-        <v>代码冗余</v>
+        <v>用户密码重置功能存在安全漏洞，重置链接未设置过期时间，可能被恶意利用，需要添加token有效期验证</v>
       </c>
       <c r="C111" t="str">
-        <v>吴十</v>
+        <v>陈七</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-22</v>
       </c>
       <c r="E111" t="str">
-        <v>严重</v>
+        <v>一般</v>
       </c>
       <c r="F111" t="str">
-        <v>根因：测试用例不足，预计解决时间：2026-04-26</v>
+        <v>【暂不处理】预计需要2个开发工作日完成修复，包含测试和回归验证。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="112">
@@ -2624,19 +2624,19 @@
         <v>T-BUG-031</v>
       </c>
       <c r="B112" t="str">
-        <v>代码冗余</v>
+        <v>用户列表页面在小屏幕设备上样式错乱，表格列重叠，需要优化响应式布局和媒体查询设置</v>
       </c>
       <c r="C112" t="str">
-        <v>王二</v>
+        <v>钱七</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E112" t="str">
-        <v>一般</v>
+        <v>严重</v>
       </c>
       <c r="F112" t="str">
-        <v/>
+        <v>预计需要2个开发工作日完成修复，包含测试和回归验证</v>
       </c>
     </row>
     <row r="113">
@@ -2644,19 +2644,19 @@
         <v>T-BUG-032</v>
       </c>
       <c r="B113" t="str">
-        <v>安全漏洞</v>
+        <v>首页加载性能问题严重，首屏渲染时间超过5秒，需要优化图片压缩、开启懒加载和代码分割</v>
       </c>
       <c r="C113" t="str">
-        <v>郑一</v>
+        <v>刘六</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E113" t="str">
         <v>提示</v>
       </c>
       <c r="F113" t="str">
-        <v/>
+        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险</v>
       </c>
     </row>
     <row r="114">
@@ -2664,19 +2664,19 @@
         <v>T-BUG-033</v>
       </c>
       <c r="B114" t="str">
-        <v>部署失败</v>
+        <v>代码冗余严重，多个组件存在重复逻辑，需要抽取公共组件和工具函数，提高代码复用率</v>
       </c>
       <c r="C114" t="str">
-        <v>黄五</v>
+        <v>刘六</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-22</v>
       </c>
       <c r="E114" t="str">
-        <v>严重</v>
+        <v>一般</v>
       </c>
       <c r="F114" t="str">
-        <v>根因：数据库连接失败，预计解决时间：2026-04-26</v>
+        <v>已修复并发布到测试环境，等待测试验证。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="115">
@@ -2684,19 +2684,19 @@
         <v>T-BUG-034</v>
       </c>
       <c r="B115" t="str">
-        <v>API接口错误</v>
+        <v>订单状态流转逻辑错误，已取消的订单仍能继续支付，需要修复状态机转换规则</v>
       </c>
       <c r="C115" t="str">
-        <v>黄五</v>
+        <v>林四</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-29</v>
       </c>
       <c r="E115" t="str">
-        <v>提示</v>
+        <v>一般</v>
       </c>
       <c r="F115" t="str">
-        <v>根因：逻辑错误，预计解决时间：2026-04-26</v>
+        <v>代码review已通过，等待合并到主分支。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="116">
@@ -2704,19 +2704,19 @@
         <v>T-BUG-035</v>
       </c>
       <c r="B116" t="str">
-        <v>数据库连接失败</v>
+        <v>用户注册API接口返回400错误，参数验证失败，需要检查请求参数格式和后端验证逻辑是否匹配</v>
       </c>
       <c r="C116" t="str">
-        <v>杨八</v>
+        <v>陈七</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E116" t="str">
-        <v>一般</v>
+        <v>提示</v>
       </c>
       <c r="F116" t="str">
-        <v>[deferred] 根因：代码冗余，预计解决时间：2026-04-26</v>
+        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险</v>
       </c>
     </row>
     <row r="117">
@@ -2724,19 +2724,19 @@
         <v>T-BUG-036</v>
       </c>
       <c r="B117" t="str">
-        <v>数据加载失败</v>
+        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
       </c>
       <c r="C117" t="str">
-        <v>黄五</v>
+        <v>刘六</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E117" t="str">
         <v>致命</v>
       </c>
       <c r="F117" t="str">
-        <v>根因：代码冗余，预计解决时间：2026-04-26</v>
+        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险。已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="118">
@@ -2744,19 +2744,19 @@
         <v>T-BUG-037</v>
       </c>
       <c r="B118" t="str">
-        <v>逻辑错误</v>
+        <v>用户列表页面在小屏幕设备上样式错乱，表格列重叠，需要优化响应式布局和媒体查询设置</v>
       </c>
       <c r="C118" t="str">
-        <v>陈七</v>
+        <v>黄五</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-29</v>
       </c>
       <c r="E118" t="str">
-        <v>一般</v>
+        <v>严重</v>
       </c>
       <c r="F118" t="str">
-        <v>[暂不处理] 根因：数据库连接失败，预计解决时间：2026-04-26</v>
+        <v>该问题已在测试环境复现，正在编写修复方案</v>
       </c>
     </row>
     <row r="119">
@@ -2764,19 +2764,19 @@
         <v>T-BUG-038</v>
       </c>
       <c r="B119" t="str">
-        <v>性能问题</v>
+        <v>代码冗余严重，多个组件存在重复逻辑，需要抽取公共组件和工具函数，提高代码复用率</v>
       </c>
       <c r="C119" t="str">
-        <v>刘六</v>
+        <v>黄五</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-29</v>
       </c>
       <c r="E119" t="str">
-        <v>致命</v>
+        <v>提示</v>
       </c>
       <c r="F119" t="str">
-        <v/>
+        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="120">
@@ -2784,19 +2784,19 @@
         <v>T-BUG-039</v>
       </c>
       <c r="B120" t="str">
-        <v>权限问题</v>
+        <v>用户注册API接口返回400错误，参数验证失败，需要检查请求参数格式和后端验证逻辑是否匹配</v>
       </c>
       <c r="C120" t="str">
-        <v>钱七</v>
+        <v>黄五</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E120" t="str">
-        <v>一般</v>
+        <v>提示</v>
       </c>
       <c r="F120" t="str">
-        <v/>
+        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="121">
@@ -2804,19 +2804,19 @@
         <v>T-BUG-040</v>
       </c>
       <c r="B121" t="str">
-        <v>缓存失效</v>
+        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
       </c>
       <c r="C121" t="str">
-        <v>孙八</v>
+        <v>周九</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-04-17</v>
+        <v>2026-05-01</v>
       </c>
       <c r="E121" t="str">
-        <v>致命</v>
+        <v>提示</v>
       </c>
       <c r="F121" t="str">
-        <v/>
+        <v>【暂不处理】需要与产品确认需求细节，当前需求描述不够清晰。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-03</v>
       </c>
     </row>
   </sheetData>

--- a/today_issues.xlsx
+++ b/today_issues.xlsx
@@ -397,2431 +397,2916 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:G121"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>链接</v>
+      </c>
+      <c r="B1" t="str">
         <v>问题单号</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>问题描述</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>开发负责人</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>创建时间</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>严重程度</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>备注</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Y-BUG-021</v>
+        <v>打开</v>
       </c>
       <c r="B2" t="str">
-        <v>用户密码重置功能存在安全漏洞，重置链接未设置过期时间，可能被恶意利用，需要添加token有效期验证</v>
+        <v>Y-BUG-032</v>
       </c>
       <c r="C2" t="str">
-        <v>赵六</v>
+        <v>用户注册API接口返回400错误，参数验证失败，需要检查请求参数格式和后端验证逻辑是否匹配</v>
       </c>
       <c r="D2" t="str">
+        <v>林四</v>
+      </c>
+      <c r="E2" t="str">
         <v>2026-04-22</v>
       </c>
-      <c r="E2" t="str">
-        <v>致命</v>
-      </c>
       <c r="F2" t="str">
-        <v>该问题已在测试环境复现，正在编写修复方案</v>
+        <v>一般</v>
+      </c>
+      <c r="G2" t="str">
+        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。需要升级依赖库版本，但可能影响其他模块，需要评估风险。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Y-BUG-015</v>
+        <v>打开</v>
       </c>
       <c r="B3" t="str">
-        <v>CI/CD部署失败，Docker镜像构建超时，需要优化构建脚本和依赖下载速度</v>
+        <v>Y-BUG-058</v>
       </c>
       <c r="C3" t="str">
-        <v>赵六</v>
+        <v>订单状态流转逻辑错误，已取消的订单仍能继续支付，需要修复状态机转换规则</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-25</v>
+        <v>林四</v>
       </c>
       <c r="E3" t="str">
-        <v>严重</v>
+        <v>2026-04-23</v>
       </c>
       <c r="F3" t="str">
-        <v>代码review已通过，等待合并到主分支</v>
+        <v>提示</v>
+      </c>
+      <c r="G3" t="str">
+        <v>该问题已在测试环境复现，正在编写修复方案。已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Y-BUG-038</v>
+        <v>打开</v>
       </c>
       <c r="B4" t="str">
-        <v>用户密码重置功能存在安全漏洞，重置链接未设置过期时间，可能被恶意利用，需要添加token有效期验证</v>
+        <v>Y-BUG-020</v>
       </c>
       <c r="C4" t="str">
-        <v>孙八</v>
+        <v>用户列表页面在小屏幕设备上样式错乱，表格列重叠，需要优化响应式布局和媒体查询设置</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-24</v>
+        <v>刘六</v>
       </c>
       <c r="E4" t="str">
-        <v>严重</v>
+        <v>2026-04-26</v>
       </c>
       <c r="F4" t="str">
-        <v>需要与产品确认需求细节，当前需求描述不够清晰</v>
+        <v>一般</v>
+      </c>
+      <c r="G4" t="str">
+        <v>【暂不处理】预计需要2个开发工作日完成修复，包含测试和回归验证。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Y-BUG-006</v>
+        <v>打开</v>
       </c>
       <c r="B5" t="str">
-        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
+        <v>Y-BUG-056</v>
       </c>
       <c r="C5" t="str">
+        <v>报表导出功能模块缺失，用户无法导出Excel格式的统计报表，需要新增导出功能组件和后端接口</v>
+      </c>
+      <c r="D5" t="str">
         <v>林四</v>
       </c>
-      <c r="D5" t="str">
-        <v>2026-04-25</v>
-      </c>
       <c r="E5" t="str">
-        <v>严重</v>
+        <v>2026-04-29</v>
       </c>
       <c r="F5" t="str">
-        <v>代码review已通过，等待合并到主分支</v>
+        <v>致命</v>
+      </c>
+      <c r="G5" t="str">
+        <v>该问题是已知问题，已列入后续迭代计划。已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Y-BUG-043</v>
+        <v>打开</v>
       </c>
       <c r="B6" t="str">
+        <v>Y-BUG-008</v>
+      </c>
+      <c r="C6" t="str">
         <v>数据库连接池在高并发场景下出现连接耗尽，需要增加连接池最大连接数配置和连接回收机制</v>
       </c>
-      <c r="C6" t="str">
+      <c r="D6" t="str">
         <v>吴十</v>
       </c>
-      <c r="D6" t="str">
-        <v>2026-05-01</v>
-      </c>
       <c r="E6" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="F6" t="str">
         <v>一般</v>
       </c>
-      <c r="F6" t="str">
-        <v>需要与产品确认需求细节，当前需求描述不够清晰。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-04</v>
+      <c r="G6" t="str">
+        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Y-BUG-031</v>
+        <v>打开</v>
       </c>
       <c r="B7" t="str">
-        <v>订单状态流转逻辑错误，已取消的订单仍能继续支付，需要修复状态机转换规则</v>
+        <v>Y-BUG-027</v>
       </c>
       <c r="C7" t="str">
-        <v>杨八</v>
+        <v>用户列表页面在小屏幕设备上样式错乱，表格列重叠，需要优化响应式布局和媒体查询设置</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-21</v>
+        <v>吴十</v>
       </c>
       <c r="E7" t="str">
-        <v>严重</v>
+        <v>2026-04-22</v>
       </c>
       <c r="F7" t="str">
-        <v>【pending】该问题已在测试环境复现，正在编写修复方案。代码review已通过，等待合并到主分支。预计解决时间：2026-05-03</v>
+        <v>致命</v>
+      </c>
+      <c r="G7" t="str">
+        <v>该问题已在测试环境复现，正在编写修复方案。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Y-BUG-044</v>
+        <v>打开</v>
       </c>
       <c r="B8" t="str">
-        <v>iOS端App在iOS 15以下版本兼容性问题，某些功能按钮点击无响应，需要检查事件绑定方式</v>
+        <v>Y-BUG-012</v>
       </c>
       <c r="C8" t="str">
-        <v>赵六</v>
+        <v>首页加载性能问题严重，首屏渲染时间超过5秒，需要优化图片压缩、开启懒加载和代码分割</v>
       </c>
       <c r="D8" t="str">
+        <v>钱七</v>
+      </c>
+      <c r="E8" t="str">
         <v>2026-04-21</v>
       </c>
-      <c r="E8" t="str">
-        <v>严重</v>
-      </c>
       <c r="F8" t="str">
-        <v>【长期跟踪】需要与产品确认需求细节，当前需求描述不够清晰。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-05</v>
+        <v>致命</v>
+      </c>
+      <c r="G8" t="str">
+        <v>需要与产品确认需求细节，当前需求描述不够清晰</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Y-BUG-005</v>
+        <v>打开</v>
       </c>
       <c r="B9" t="str">
-        <v>用户反馈弹窗关闭按钮位置不合理，用户容易误触，需要优化UI布局和交互体验</v>
+        <v>Y-BUG-002</v>
       </c>
       <c r="C9" t="str">
-        <v>陈七</v>
+        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-29</v>
+        <v>王五</v>
       </c>
       <c r="E9" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="F9" t="str">
         <v>提示</v>
       </c>
-      <c r="F9" t="str">
-        <v>【deferred】需要与产品确认需求细节，当前需求描述不够清晰。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-08</v>
+      <c r="G9" t="str">
+        <v>【长期跟踪】该问题是已知问题，已列入后续迭代计划。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Y-BUG-048</v>
+        <v>打开</v>
       </c>
       <c r="B10" t="str">
-        <v>报表导出功能模块缺失，用户无法导出Excel格式的统计报表，需要新增导出功能组件和后端接口</v>
+        <v>Y-BUG-067</v>
       </c>
       <c r="C10" t="str">
-        <v>林四</v>
+        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-22</v>
+        <v>赵六</v>
       </c>
       <c r="E10" t="str">
-        <v>严重</v>
+        <v>2026-04-29</v>
       </c>
       <c r="F10" t="str">
-        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计需要2个开发工作日完成修复，包含测试和回归验证。预计解决时间：2026-05-05</v>
+        <v>提示</v>
+      </c>
+      <c r="G10" t="str">
+        <v>【deferred】涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计需要2个开发工作日完成修复，包含测试和回归验证。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Y-BUG-019</v>
+        <v>打开</v>
       </c>
       <c r="B11" t="str">
-        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
+        <v>Y-BUG-040</v>
       </c>
       <c r="C11" t="str">
-        <v>孙八</v>
+        <v>代码冗余严重，多个组件存在重复逻辑，需要抽取公共组件和工具函数，提高代码复用率</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-25</v>
+        <v>郑一</v>
       </c>
       <c r="E11" t="str">
-        <v>提示</v>
+        <v>2026-05-01</v>
       </c>
       <c r="F11" t="str">
-        <v>需要与产品确认需求细节，当前需求描述不够清晰。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-03</v>
+        <v>严重</v>
+      </c>
+      <c r="G11" t="str">
+        <v>【deferred】需要升级依赖库版本，但可能影响其他模块，需要评估风险。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Y-BUG-022</v>
+        <v>打开</v>
       </c>
       <c r="B12" t="str">
-        <v>测试用例覆盖率不足60%，核心功能缺少单元测试，需要补充测试用例确保代码质量</v>
+        <v>Y-BUG-023</v>
       </c>
       <c r="C12" t="str">
-        <v>郑一</v>
+        <v>报表导出功能模块缺失，用户无法导出Excel格式的统计报表，需要新增导出功能组件和后端接口</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-29</v>
+        <v>林四</v>
       </c>
       <c r="E12" t="str">
-        <v>致命</v>
+        <v>2026-04-30</v>
       </c>
       <c r="F12" t="str">
-        <v>【长期跟踪】该问题是已知问题，已列入后续迭代计划。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-03</v>
+        <v>一般</v>
+      </c>
+      <c r="G12" t="str">
+        <v>【跟踪中】需要与产品确认需求细节，当前需求描述不够清晰。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Y-BUG-032</v>
+        <v>打开</v>
       </c>
       <c r="B13" t="str">
-        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
+        <v>Y-BUG-034</v>
       </c>
       <c r="C13" t="str">
-        <v>陈七</v>
+        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
       </c>
       <c r="D13" t="str">
+        <v>郑一</v>
+      </c>
+      <c r="E13" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="E13" t="str">
-        <v>提示</v>
-      </c>
       <c r="F13" t="str">
-        <v>【暂不处理】涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计解决时间：2026-05-05</v>
+        <v>一般</v>
+      </c>
+      <c r="G13" t="str">
+        <v>【deferred】需要与产品确认需求细节，当前需求描述不够清晰。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Y-BUG-009</v>
+        <v>打开</v>
       </c>
       <c r="B14" t="str">
-        <v>首页数据加载失败，显示空白页面，经检查是接口返回数据格式变更导致JSON解析错误，需要更新数据解析逻辑</v>
+        <v>Y-BUG-041</v>
       </c>
       <c r="C14" t="str">
-        <v>周九</v>
+        <v>配置文件管理混乱，开发环境和生产环境配置混用，需要建立统一的配置管理方案</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-28</v>
+        <v>陈三</v>
       </c>
       <c r="E14" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="F14" t="str">
         <v>致命</v>
       </c>
-      <c r="F14" t="str">
-        <v>代码review已通过，等待合并到主分支。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-05</v>
+      <c r="G14" t="str">
+        <v>该问题已在测试环境复现，正在编写修复方案</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Y-BUG-008</v>
+        <v>打开</v>
       </c>
       <c r="B15" t="str">
-        <v>支付功能在移动端提交订单时出现网络超时错误，经排查发现是API请求超时时间设置过短，需要调整axios的timeout配置</v>
+        <v>Y-BUG-060</v>
       </c>
       <c r="C15" t="str">
-        <v>王五</v>
+        <v>用户列表页面在小屏幕设备上样式错乱，表格列重叠，需要优化响应式布局和媒体查询设置</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-30</v>
+        <v>刘六</v>
       </c>
       <c r="E15" t="str">
-        <v>提示</v>
+        <v>2026-04-28</v>
       </c>
       <c r="F15" t="str">
-        <v>【跟踪中】已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计需要2个开发工作日完成修复，包含测试和回归验证。预计解决时间：2026-05-05</v>
+        <v>一般</v>
+      </c>
+      <c r="G15" t="str">
+        <v>该问题已在测试环境复现，正在编写修复方案</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Y-BUG-012</v>
+        <v>打开</v>
       </c>
       <c r="B16" t="str">
-        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
+        <v>Y-BUG-075</v>
       </c>
       <c r="C16" t="str">
-        <v>李四</v>
+        <v>首页加载性能问题严重，首屏渲染时间超过5秒，需要优化图片压缩、开启懒加载和代码分割</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-30</v>
+        <v>吴十</v>
       </c>
       <c r="E16" t="str">
-        <v>一般</v>
+        <v>2026-04-27</v>
       </c>
       <c r="F16" t="str">
-        <v>【跟踪中】需要升级依赖库版本，但可能影响其他模块，需要评估风险。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-09</v>
+        <v>严重</v>
+      </c>
+      <c r="G16" t="str">
+        <v>该问题已在测试环境复现，正在编写修复方案</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Y-BUG-025</v>
+        <v>打开</v>
       </c>
       <c r="B17" t="str">
-        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
+        <v>Y-BUG-036</v>
       </c>
       <c r="C17" t="str">
-        <v>刘六</v>
+        <v>用户注册API接口返回400错误，参数验证失败，需要检查请求参数格式和后端验证逻辑是否匹配</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-25</v>
+        <v>郑一</v>
       </c>
       <c r="E17" t="str">
-        <v>提示</v>
+        <v>2026-04-30</v>
       </c>
       <c r="F17" t="str">
-        <v>【暂不处理】已经定位到问题根因，是由于异步请求时序问题导致状态不一致。已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计解决时间：2026-05-09</v>
+        <v>一般</v>
+      </c>
+      <c r="G17" t="str">
+        <v>【跟踪中】代码review已通过，等待合并到主分支。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-06</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Y-BUG-007</v>
+        <v>打开</v>
       </c>
       <c r="B18" t="str">
-        <v>支付功能在移动端提交订单时出现网络超时错误，经排查发现是API请求超时时间设置过短，需要调整axios的timeout配置</v>
+        <v>Y-BUG-099</v>
       </c>
       <c r="C18" t="str">
-        <v>陈七</v>
+        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-27</v>
+        <v>吴十</v>
       </c>
       <c r="E18" t="str">
-        <v>严重</v>
+        <v>2026-04-30</v>
       </c>
       <c r="F18" t="str">
-        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-05</v>
+        <v>一般</v>
+      </c>
+      <c r="G18" t="str">
+        <v>已修复并发布到测试环境，等待测试验证</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Y-BUG-039</v>
+        <v>打开</v>
       </c>
       <c r="B19" t="str">
-        <v>Redis缓存失效导致频繁查询数据库，需要检查缓存更新策略和过期时间设置</v>
+        <v>Y-BUG-035</v>
       </c>
       <c r="C19" t="str">
-        <v>钱七</v>
+        <v>用户反馈弹窗关闭按钮位置不合理，用户容易误触，需要优化UI布局和交互体验</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-26</v>
+        <v>陈七</v>
       </c>
       <c r="E19" t="str">
-        <v>提示</v>
+        <v>2026-04-28</v>
       </c>
       <c r="F19" t="str">
-        <v>代码review已通过，等待合并到主分支</v>
+        <v>致命</v>
+      </c>
+      <c r="G19" t="str">
+        <v>【长期跟踪】涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Y-BUG-020</v>
+        <v>打开</v>
       </c>
       <c r="B20" t="str">
-        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
+        <v>Y-BUG-059</v>
       </c>
       <c r="C20" t="str">
-        <v>刘六</v>
+        <v>CI/CD部署失败，Docker镜像构建超时，需要优化构建脚本和依赖下载速度</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-22</v>
+        <v>林四</v>
       </c>
       <c r="E20" t="str">
-        <v>严重</v>
+        <v>2026-04-25</v>
       </c>
       <c r="F20" t="str">
-        <v>【pending】经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-06</v>
+        <v>提示</v>
+      </c>
+      <c r="G20" t="str">
+        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Y-BUG-050</v>
+        <v>打开</v>
       </c>
       <c r="B21" t="str">
-        <v>首页数据加载失败，显示空白页面，经检查是接口返回数据格式变更导致JSON解析错误，需要更新数据解析逻辑</v>
+        <v>Y-BUG-055</v>
       </c>
       <c r="C21" t="str">
-        <v>张三</v>
+        <v>配置文件管理混乱，开发环境和生产环境配置混用，需要建立统一的配置管理方案</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-24</v>
+        <v>李四</v>
       </c>
       <c r="E21" t="str">
-        <v>提示</v>
+        <v>2026-04-26</v>
       </c>
       <c r="F21" t="str">
-        <v>预计需要2个开发工作日完成修复，包含测试和回归验证。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-03</v>
+        <v>致命</v>
+      </c>
+      <c r="G21" t="str">
+        <v>【跟踪中】该问题已在测试环境复现，正在编写修复方案。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-09</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Y-BUG-045</v>
+        <v>打开</v>
       </c>
       <c r="B22" t="str">
-        <v>用户注册API接口返回400错误，参数验证失败，需要检查请求参数格式和后端验证逻辑是否匹配</v>
+        <v>Y-BUG-006</v>
       </c>
       <c r="C22" t="str">
-        <v>周九</v>
+        <v>代码冗余严重，多个组件存在重复逻辑，需要抽取公共组件和工具函数，提高代码复用率</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-23</v>
+        <v>孙八</v>
       </c>
       <c r="E22" t="str">
-        <v>致命</v>
+        <v>2026-04-28</v>
       </c>
       <c r="F22" t="str">
-        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致</v>
+        <v>提示</v>
+      </c>
+      <c r="G22" t="str">
+        <v>【暂不处理】预计需要2个开发工作日完成修复，包含测试和回归验证。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-07</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Y-BUG-046</v>
+        <v>打开</v>
       </c>
       <c r="B23" t="str">
-        <v>报表导出功能模块缺失，用户无法导出Excel格式的统计报表，需要新增导出功能组件和后端接口</v>
+        <v>Y-BUG-076</v>
       </c>
       <c r="C23" t="str">
-        <v>钱七</v>
+        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-22</v>
+        <v>陈七</v>
       </c>
       <c r="E23" t="str">
-        <v>提示</v>
+        <v>2026-04-25</v>
       </c>
       <c r="F23" t="str">
-        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-03</v>
+        <v>严重</v>
+      </c>
+      <c r="G23" t="str">
+        <v>【跟踪中】经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。代码review已通过，等待合并到主分支。预计解决时间：2026-05-08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Y-BUG-004</v>
+        <v>打开</v>
       </c>
       <c r="B24" t="str">
-        <v>配置文件管理混乱，开发环境和生产环境配置混用，需要建立统一的配置管理方案</v>
+        <v>Y-BUG-029</v>
       </c>
       <c r="C24" t="str">
-        <v>王五</v>
+        <v>报表导出功能模块缺失，用户无法导出Excel格式的统计报表，需要新增导出功能组件和后端接口</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-23</v>
+        <v>孙八</v>
       </c>
       <c r="E24" t="str">
-        <v>提示</v>
+        <v>2026-04-21</v>
       </c>
       <c r="F24" t="str">
-        <v>预计需要2个开发工作日完成修复，包含测试和回归验证</v>
+        <v>一般</v>
+      </c>
+      <c r="G24" t="str">
+        <v>【长期跟踪】需要升级依赖库版本，但可能影响其他模块，需要评估风险。预计需要2个开发工作日完成修复，包含测试和回归验证。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Y-BUG-003</v>
+        <v>打开</v>
       </c>
       <c r="B25" t="str">
-        <v>用户列表页面在小屏幕设备上样式错乱，表格列重叠，需要优化响应式布局和媒体查询设置</v>
+        <v>Y-BUG-004</v>
       </c>
       <c r="C25" t="str">
-        <v>李四</v>
+        <v>用户密码重置功能存在安全漏洞，重置链接未设置过期时间，可能被恶意利用，需要添加token有效期验证</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-01</v>
+        <v>郑一</v>
       </c>
       <c r="E25" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="F25" t="str">
         <v>严重</v>
       </c>
-      <c r="F25" t="str">
-        <v>预计需要2个开发工作日完成修复，包含测试和回归验证。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-05</v>
+      <c r="G25" t="str">
+        <v>【pending】经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-09</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Y-BUG-030</v>
+        <v>打开</v>
       </c>
       <c r="B26" t="str">
-        <v>报表导出功能模块缺失，用户无法导出Excel格式的统计报表，需要新增导出功能组件和后端接口</v>
+        <v>Y-BUG-007</v>
       </c>
       <c r="C26" t="str">
+        <v>代码冗余严重，多个组件存在重复逻辑，需要抽取公共组件和工具函数，提高代码复用率</v>
+      </c>
+      <c r="D26" t="str">
         <v>李四</v>
       </c>
-      <c r="D26" t="str">
-        <v>2026-04-22</v>
-      </c>
       <c r="E26" t="str">
-        <v>严重</v>
+        <v>2026-04-27</v>
       </c>
       <c r="F26" t="str">
-        <v>【长期跟踪】该问题已在测试环境复现，正在编写修复方案。需要升级依赖库版本，但可能影响其他模块，需要评估风险。预计解决时间：2026-05-09</v>
+        <v>致命</v>
+      </c>
+      <c r="G26" t="str">
+        <v>代码review已通过，等待合并到主分支</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Y-BUG-010</v>
+        <v>打开</v>
       </c>
       <c r="B27" t="str">
+        <v>Y-BUG-001</v>
+      </c>
+      <c r="C27" t="str">
         <v>测试用例覆盖率不足60%，核心功能缺少单元测试，需要补充测试用例确保代码质量</v>
       </c>
-      <c r="C27" t="str">
-        <v>林四</v>
-      </c>
       <c r="D27" t="str">
-        <v>2026-04-27</v>
+        <v>吴十</v>
       </c>
       <c r="E27" t="str">
-        <v>严重</v>
+        <v>2026-04-21</v>
       </c>
       <c r="F27" t="str">
-        <v>需要与产品确认需求细节，当前需求描述不够清晰</v>
+        <v>致命</v>
+      </c>
+      <c r="G27" t="str">
+        <v>【pending】已经定位到问题根因，是由于异步请求时序问题导致状态不一致。需要升级依赖库版本，但可能影响其他模块，需要评估风险。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Y-BUG-014</v>
+        <v>打开</v>
       </c>
       <c r="B28" t="str">
-        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
+        <v>Y-BUG-090</v>
       </c>
       <c r="C28" t="str">
-        <v>刘六</v>
+        <v>首页加载性能问题严重，首屏渲染时间超过5秒，需要优化图片压缩、开启懒加载和代码分割</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-26</v>
+        <v>吴十</v>
       </c>
       <c r="E28" t="str">
-        <v>致命</v>
+        <v>2026-04-23</v>
       </c>
       <c r="F28" t="str">
-        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-03</v>
+        <v>严重</v>
+      </c>
+      <c r="G28" t="str">
+        <v>【pending】预计需要2个开发工作日完成修复，包含测试和回归验证。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Y-BUG-011</v>
+        <v>打开</v>
       </c>
       <c r="B29" t="str">
-        <v>测试用例覆盖率不足60%，核心功能缺少单元测试，需要补充测试用例确保代码质量</v>
+        <v>Y-BUG-054</v>
       </c>
       <c r="C29" t="str">
-        <v>赵六</v>
+        <v>用户密码重置功能存在安全漏洞，重置链接未设置过期时间，可能被恶意利用，需要添加token有效期验证</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-21</v>
+        <v>吴十</v>
       </c>
       <c r="E29" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="F29" t="str">
         <v>提示</v>
       </c>
-      <c r="F29" t="str">
-        <v>【长期跟踪】该问题是已知问题，已列入后续迭代计划。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-05</v>
+      <c r="G29" t="str">
+        <v>【pending】涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。需要升级依赖库版本，但可能影响其他模块，需要评估风险。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Y-BUG-002</v>
+        <v>打开</v>
       </c>
       <c r="B30" t="str">
-        <v>用户密码重置功能存在安全漏洞，重置链接未设置过期时间，可能被恶意利用，需要添加token有效期验证</v>
+        <v>Y-BUG-071</v>
       </c>
       <c r="C30" t="str">
-        <v>陈三</v>
+        <v>iOS端App在iOS 15以下版本兼容性问题，某些功能按钮点击无响应，需要检查事件绑定方式</v>
       </c>
       <c r="D30" t="str">
+        <v>王五</v>
+      </c>
+      <c r="E30" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="E30" t="str">
-        <v>致命</v>
-      </c>
       <c r="F30" t="str">
-        <v>该问题是已知问题，已列入后续迭代计划。需要升级依赖库版本，但可能影响其他模块，需要评估风险。预计解决时间：2026-05-05</v>
+        <v>一般</v>
+      </c>
+      <c r="G30" t="str">
+        <v>该问题是已知问题，已列入后续迭代计划</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Y-BUG-037</v>
+        <v>打开</v>
       </c>
       <c r="B31" t="str">
-        <v>测试用例覆盖率不足60%，核心功能缺少单元测试，需要补充测试用例确保代码质量</v>
+        <v>Y-BUG-048</v>
       </c>
       <c r="C31" t="str">
-        <v>钱七</v>
+        <v>订单状态流转逻辑错误，已取消的订单仍能继续支付，需要修复状态机转换规则</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-27</v>
+        <v>陈七</v>
       </c>
       <c r="E31" t="str">
-        <v>一般</v>
+        <v>2026-04-22</v>
       </c>
       <c r="F31" t="str">
-        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-05</v>
+        <v>致命</v>
+      </c>
+      <c r="G31" t="str">
+        <v>已修复并发布到测试环境，等待测试验证。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Y-BUG-035</v>
+        <v>打开</v>
       </c>
       <c r="B32" t="str">
+        <v>Y-BUG-068</v>
+      </c>
+      <c r="C32" t="str">
         <v>用户权限验证逻辑存在漏洞，普通用户可以访问管理员页面，需要加强路由守卫和权限检查</v>
       </c>
-      <c r="C32" t="str">
-        <v>黄五</v>
-      </c>
       <c r="D32" t="str">
-        <v>2026-04-24</v>
+        <v>赵六</v>
       </c>
       <c r="E32" t="str">
-        <v>一般</v>
+        <v>2026-04-26</v>
       </c>
       <c r="F32" t="str">
-        <v>【pending】经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-08</v>
+        <v>严重</v>
+      </c>
+      <c r="G32" t="str">
+        <v>经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Y-BUG-026</v>
+        <v>打开</v>
       </c>
       <c r="B33" t="str">
+        <v>Y-BUG-063</v>
+      </c>
+      <c r="C33" t="str">
         <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
       </c>
-      <c r="C33" t="str">
-        <v>钱七</v>
-      </c>
       <c r="D33" t="str">
-        <v>2026-04-27</v>
+        <v>孙八</v>
       </c>
       <c r="E33" t="str">
-        <v>提示</v>
+        <v>2026-04-26</v>
       </c>
       <c r="F33" t="str">
-        <v>【暂不处理】需要与产品确认需求细节，当前需求描述不够清晰。已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计解决时间：2026-05-09</v>
+        <v>致命</v>
+      </c>
+      <c r="G33" t="str">
+        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Y-BUG-027</v>
+        <v>打开</v>
       </c>
       <c r="B34" t="str">
-        <v>用户列表页面在小屏幕设备上样式错乱，表格列重叠，需要优化响应式布局和媒体查询设置</v>
+        <v>Y-BUG-082</v>
       </c>
       <c r="C34" t="str">
-        <v>陈七</v>
+        <v>CI/CD部署失败，Docker镜像构建超时，需要优化构建脚本和依赖下载速度</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-01</v>
+        <v>郑一</v>
       </c>
       <c r="E34" t="str">
-        <v>提示</v>
+        <v>2026-04-26</v>
       </c>
       <c r="F34" t="str">
-        <v>代码review已通过，等待合并到主分支</v>
+        <v>严重</v>
+      </c>
+      <c r="G34" t="str">
+        <v>该问题已在测试环境复现，正在编写修复方案</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Y-BUG-017</v>
+        <v>打开</v>
       </c>
       <c r="B35" t="str">
-        <v>报表导出功能模块缺失，用户无法导出Excel格式的统计报表，需要新增导出功能组件和后端接口</v>
+        <v>Y-BUG-084</v>
       </c>
       <c r="C35" t="str">
-        <v>张三</v>
+        <v>用户权限验证逻辑存在漏洞，普通用户可以访问管理员页面，需要加强路由守卫和权限检查</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-25</v>
+        <v>郑一</v>
       </c>
       <c r="E35" t="str">
-        <v>一般</v>
+        <v>2026-04-23</v>
       </c>
       <c r="F35" t="str">
-        <v>该问题已在测试环境复现，正在编写修复方案</v>
+        <v>严重</v>
+      </c>
+      <c r="G35" t="str">
+        <v>需要与产品确认需求细节，当前需求描述不够清晰</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Y-BUG-040</v>
+        <v>打开</v>
       </c>
       <c r="B36" t="str">
-        <v>支付功能在移动端提交订单时出现网络超时错误，经排查发现是API请求超时时间设置过短，需要调整axios的timeout配置</v>
+        <v>Y-BUG-026</v>
       </c>
       <c r="C36" t="str">
-        <v>刘六</v>
+        <v>用户密码重置功能存在安全漏洞，重置链接未设置过期时间，可能被恶意利用，需要添加token有效期验证</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-24</v>
+        <v>周九</v>
       </c>
       <c r="E36" t="str">
-        <v>提示</v>
+        <v>2026-04-29</v>
       </c>
       <c r="F36" t="str">
-        <v>【长期跟踪】代码review已通过，等待合并到主分支。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-07</v>
+        <v>致命</v>
+      </c>
+      <c r="G36" t="str">
+        <v>经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Y-BUG-029</v>
+        <v>打开</v>
       </c>
       <c r="B37" t="str">
-        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
+        <v>Y-BUG-070</v>
       </c>
       <c r="C37" t="str">
-        <v>孙八</v>
+        <v>Redis缓存失效导致频繁查询数据库，需要检查缓存更新策略和过期时间设置</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-01</v>
+        <v>杨八</v>
       </c>
       <c r="E37" t="str">
-        <v>致命</v>
+        <v>2026-04-25</v>
       </c>
       <c r="F37" t="str">
-        <v>预计需要2个开发工作日完成修复，包含测试和回归验证。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-04</v>
+        <v>提示</v>
+      </c>
+      <c r="G37" t="str">
+        <v>【跟踪中】该问题已在测试环境复现，正在编写修复方案。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Y-BUG-034</v>
+        <v>打开</v>
       </c>
       <c r="B38" t="str">
-        <v>首页加载性能问题严重，首屏渲染时间超过5秒，需要优化图片压缩、开启懒加载和代码分割</v>
+        <v>Y-BUG-053</v>
       </c>
       <c r="C38" t="str">
-        <v>陈七</v>
+        <v>用户注册API接口返回400错误，参数验证失败，需要检查请求参数格式和后端验证逻辑是否匹配</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-30</v>
+        <v>赵六</v>
       </c>
       <c r="E38" t="str">
-        <v>提示</v>
+        <v>2026-05-01</v>
       </c>
       <c r="F38" t="str">
-        <v>【pending】需要与产品确认需求细节，当前需求描述不够清晰。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-09</v>
+        <v>严重</v>
+      </c>
+      <c r="G38" t="str">
+        <v>需要与产品确认需求细节，当前需求描述不够清晰</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Y-BUG-049</v>
+        <v>打开</v>
       </c>
       <c r="B39" t="str">
-        <v>用户密码重置功能存在安全漏洞，重置链接未设置过期时间，可能被恶意利用，需要添加token有效期验证</v>
+        <v>Y-BUG-098</v>
       </c>
       <c r="C39" t="str">
-        <v>赵六</v>
+        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-27</v>
+        <v>黄五</v>
       </c>
       <c r="E39" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="F39" t="str">
         <v>提示</v>
       </c>
-      <c r="F39" t="str">
-        <v>需要与产品确认需求细节，当前需求描述不够清晰</v>
+      <c r="G39" t="str">
+        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Y-BUG-042</v>
+        <v>打开</v>
       </c>
       <c r="B40" t="str">
-        <v>Redis缓存失效导致频繁查询数据库，需要检查缓存更新策略和过期时间设置</v>
+        <v>Y-BUG-033</v>
       </c>
       <c r="C40" t="str">
-        <v>林四</v>
+        <v>CI/CD部署失败，Docker镜像构建超时，需要优化构建脚本和依赖下载速度</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-22</v>
+        <v>王二</v>
       </c>
       <c r="E40" t="str">
-        <v>一般</v>
+        <v>2026-04-26</v>
       </c>
       <c r="F40" t="str">
-        <v>【deferred】代码review已通过，等待合并到主分支。预计需要2个开发工作日完成修复，包含测试和回归验证。预计解决时间：2026-05-09</v>
+        <v>提示</v>
+      </c>
+      <c r="G40" t="str">
+        <v>需要与产品确认需求细节，当前需求描述不够清晰</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Y-BUG-018</v>
+        <v>打开</v>
       </c>
       <c r="B41" t="str">
-        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
+        <v>Y-BUG-087</v>
       </c>
       <c r="C41" t="str">
+        <v>CI/CD部署失败，Docker镜像构建超时，需要优化构建脚本和依赖下载速度</v>
+      </c>
+      <c r="D41" t="str">
         <v>王二</v>
       </c>
-      <c r="D41" t="str">
-        <v>2026-04-21</v>
-      </c>
       <c r="E41" t="str">
-        <v>严重</v>
+        <v>2026-04-26</v>
       </c>
       <c r="F41" t="str">
-        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致</v>
+        <v>提示</v>
+      </c>
+      <c r="G41" t="str">
+        <v>已修复并发布到测试环境，等待测试验证。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Y-BUG-028</v>
+        <v>打开</v>
       </c>
       <c r="B42" t="str">
-        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
+        <v>Y-BUG-015</v>
       </c>
       <c r="C42" t="str">
-        <v>吴十</v>
+        <v>数据库连接池在高并发场景下出现连接耗尽，需要增加连接池最大连接数配置和连接回收机制</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-01</v>
+        <v>王五</v>
       </c>
       <c r="E42" t="str">
-        <v>提示</v>
+        <v>2026-04-23</v>
       </c>
       <c r="F42" t="str">
-        <v>需要与产品确认需求细节，当前需求描述不够清晰</v>
+        <v>一般</v>
+      </c>
+      <c r="G42" t="str">
+        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Y-BUG-001</v>
+        <v>打开</v>
       </c>
       <c r="B43" t="str">
-        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
+        <v>Y-BUG-021</v>
       </c>
       <c r="C43" t="str">
-        <v>陈三</v>
+        <v>数据库连接池在高并发场景下出现连接耗尽，需要增加连接池最大连接数配置和连接回收机制</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-25</v>
+        <v>周九</v>
       </c>
       <c r="E43" t="str">
-        <v>致命</v>
+        <v>2026-04-24</v>
       </c>
       <c r="F43" t="str">
-        <v>【长期跟踪】已修复并发布到测试环境，等待测试验证。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-04</v>
+        <v>一般</v>
+      </c>
+      <c r="G43" t="str">
+        <v>经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Y-BUG-013</v>
+        <v>打开</v>
       </c>
       <c r="B44" t="str">
-        <v>支付功能在移动端提交订单时出现网络超时错误，经排查发现是API请求超时时间设置过短，需要调整axios的timeout配置</v>
+        <v>Y-BUG-024</v>
       </c>
       <c r="C44" t="str">
-        <v>王五</v>
+        <v>测试用例覆盖率不足60%，核心功能缺少单元测试，需要补充测试用例确保代码质量</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-29</v>
+        <v>郑一</v>
       </c>
       <c r="E44" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="F44" t="str">
         <v>提示</v>
       </c>
-      <c r="F44" t="str">
-        <v>【pending】该问题已在测试环境复现，正在编写修复方案。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-04</v>
+      <c r="G44" t="str">
+        <v>【长期跟踪】预计需要2个开发工作日完成修复，包含测试和回归验证。已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计解决时间：2026-05-07</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Y-BUG-041</v>
+        <v>打开</v>
       </c>
       <c r="B45" t="str">
+        <v>Y-BUG-086</v>
+      </c>
+      <c r="C45" t="str">
         <v>数据库连接池在高并发场景下出现连接耗尽，需要增加连接池最大连接数配置和连接回收机制</v>
       </c>
-      <c r="C45" t="str">
-        <v>吴十</v>
-      </c>
       <c r="D45" t="str">
-        <v>2026-04-22</v>
+        <v>杨八</v>
       </c>
       <c r="E45" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="F45" t="str">
         <v>严重</v>
       </c>
-      <c r="F45" t="str">
-        <v>该问题是已知问题，已列入后续迭代计划</v>
+      <c r="G45" t="str">
+        <v>【跟踪中】需要与产品确认需求细节，当前需求描述不够清晰。预计需要2个开发工作日完成修复，包含测试和回归验证。预计解决时间：2026-05-09</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Y-BUG-023</v>
+        <v>打开</v>
       </c>
       <c r="B46" t="str">
-        <v>首页数据加载失败，显示空白页面，经检查是接口返回数据格式变更导致JSON解析错误，需要更新数据解析逻辑</v>
+        <v>Y-BUG-050</v>
       </c>
       <c r="C46" t="str">
-        <v>郑一</v>
+        <v>支付功能在移动端提交订单时出现网络超时错误，经排查发现是API请求超时时间设置过短，需要调整axios的timeout配置</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-26</v>
+        <v>张三</v>
       </c>
       <c r="E46" t="str">
-        <v>提示</v>
+        <v>2026-04-24</v>
       </c>
       <c r="F46" t="str">
-        <v>需要与产品确认需求细节，当前需求描述不够清晰</v>
+        <v>一般</v>
+      </c>
+      <c r="G46" t="str">
+        <v>需要与产品确认需求细节，当前需求描述不够清晰。需要升级依赖库版本，但可能影响其他模块，需要评估风险。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Y-BUG-056</v>
+        <v>打开</v>
       </c>
       <c r="B47" t="str">
-        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
+        <v>Y-BUG-064</v>
       </c>
       <c r="C47" t="str">
-        <v>钱七</v>
+        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-26</v>
+        <v>赵六</v>
       </c>
       <c r="E47" t="str">
-        <v>致命</v>
+        <v>2026-04-25</v>
       </c>
       <c r="F47" t="str">
-        <v>代码review已通过，等待合并到主分支</v>
+        <v>提示</v>
+      </c>
+      <c r="G47" t="str">
+        <v>【pending】需要升级依赖库版本，但可能影响其他模块，需要评估风险。需要升级依赖库版本，但可能影响其他模块，需要评估风险。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Y-BUG-079</v>
+        <v>打开</v>
       </c>
       <c r="B48" t="str">
-        <v>首页数据加载失败，显示空白页面，经检查是接口返回数据格式变更导致JSON解析错误，需要更新数据解析逻辑</v>
+        <v>Y-BUG-094</v>
       </c>
       <c r="C48" t="str">
-        <v>林四</v>
+        <v>用户列表页面在小屏幕设备上样式错乱，表格列重叠，需要优化响应式布局和媒体查询设置</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-26</v>
+        <v>刘六</v>
       </c>
       <c r="E48" t="str">
-        <v>一般</v>
+        <v>2026-04-28</v>
       </c>
       <c r="F48" t="str">
-        <v>经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。代码review已通过，等待合并到主分支。预计解决时间：2026-05-04</v>
+        <v>致命</v>
+      </c>
+      <c r="G48" t="str">
+        <v>【长期跟踪】经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。代码review已通过，等待合并到主分支。预计解决时间：2026-05-06</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Y-BUG-061</v>
+        <v>打开</v>
       </c>
       <c r="B49" t="str">
-        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
+        <v>Y-BUG-045</v>
       </c>
       <c r="C49" t="str">
-        <v>李四</v>
+        <v>订单状态流转逻辑错误，已取消的订单仍能继续支付，需要修复状态机转换规则</v>
       </c>
       <c r="D49" t="str">
+        <v>黄五</v>
+      </c>
+      <c r="E49" t="str">
         <v>2026-04-25</v>
       </c>
-      <c r="E49" t="str">
+      <c r="F49" t="str">
         <v>一般</v>
       </c>
-      <c r="F49" t="str">
-        <v>该问题是已知问题，已列入后续迭代计划</v>
+      <c r="G49" t="str">
+        <v>已修复并发布到测试环境，等待测试验证</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Y-BUG-024</v>
+        <v>打开</v>
       </c>
       <c r="B50" t="str">
-        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
+        <v>Y-BUG-010</v>
       </c>
       <c r="C50" t="str">
+        <v>用户权限验证逻辑存在漏洞，普通用户可以访问管理员页面，需要加强路由守卫和权限检查</v>
+      </c>
+      <c r="D50" t="str">
         <v>周九</v>
       </c>
-      <c r="D50" t="str">
-        <v>2026-04-26</v>
-      </c>
       <c r="E50" t="str">
-        <v>一般</v>
+        <v>2026-04-29</v>
       </c>
       <c r="F50" t="str">
-        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-03</v>
+        <v>致命</v>
+      </c>
+      <c r="G50" t="str">
+        <v>【跟踪中】代码review已通过，等待合并到主分支。预计需要2个开发工作日完成修复，包含测试和回归验证。预计解决时间：2026-05-06</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Y-BUG-083</v>
+        <v>打开</v>
       </c>
       <c r="B51" t="str">
-        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
+        <v>Y-BUG-052</v>
       </c>
       <c r="C51" t="str">
-        <v>张三</v>
+        <v>报表导出功能模块缺失，用户无法导出Excel格式的统计报表，需要新增导出功能组件和后端接口</v>
       </c>
       <c r="D51" t="str">
+        <v>陈三</v>
+      </c>
+      <c r="E51" t="str">
         <v>2026-04-22</v>
       </c>
-      <c r="E51" t="str">
-        <v>致命</v>
-      </c>
       <c r="F51" t="str">
-        <v>【暂不处理】该问题已在测试环境复现，正在编写修复方案。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-04</v>
+        <v>一般</v>
+      </c>
+      <c r="G51" t="str">
+        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Y-BUG-086</v>
+        <v>打开</v>
       </c>
       <c r="B52" t="str">
-        <v>配置文件管理混乱，开发环境和生产环境配置混用，需要建立统一的配置管理方案</v>
+        <v>Y-BUG-003</v>
       </c>
       <c r="C52" t="str">
-        <v>陈三</v>
+        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
       </c>
       <c r="D52" t="str">
+        <v>赵六</v>
+      </c>
+      <c r="E52" t="str">
         <v>2026-04-23</v>
       </c>
-      <c r="E52" t="str">
-        <v>致命</v>
-      </c>
       <c r="F52" t="str">
-        <v>经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查</v>
+        <v>严重</v>
+      </c>
+      <c r="G52" t="str">
+        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Y-BUG-054</v>
+        <v>打开</v>
       </c>
       <c r="B53" t="str">
-        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
+        <v>Y-BUG-074</v>
       </c>
       <c r="C53" t="str">
-        <v>王二</v>
+        <v>测试用例覆盖率不足60%，核心功能缺少单元测试，需要补充测试用例确保代码质量</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-26</v>
+        <v>赵六</v>
       </c>
       <c r="E53" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="F53" t="str">
         <v>严重</v>
       </c>
-      <c r="F53" t="str">
-        <v>已修复并发布到测试环境，等待测试验证</v>
+      <c r="G53" t="str">
+        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Y-BUG-053</v>
+        <v>打开</v>
       </c>
       <c r="B54" t="str">
-        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
+        <v>Y-BUG-062</v>
       </c>
       <c r="C54" t="str">
+        <v>测试用例覆盖率不足60%，核心功能缺少单元测试，需要补充测试用例确保代码质量</v>
+      </c>
+      <c r="D54" t="str">
         <v>刘六</v>
       </c>
-      <c r="D54" t="str">
-        <v>2026-05-01</v>
-      </c>
       <c r="E54" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="F54" t="str">
         <v>严重</v>
       </c>
-      <c r="F54" t="str">
-        <v>该问题是已知问题，已列入后续迭代计划。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-05</v>
+      <c r="G54" t="str">
+        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Y-BUG-072</v>
+        <v>打开</v>
       </c>
       <c r="B55" t="str">
-        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
+        <v>Y-BUG-092</v>
       </c>
       <c r="C55" t="str">
-        <v>钱七</v>
+        <v>Redis缓存失效导致频繁查询数据库，需要检查缓存更新策略和过期时间设置</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-27</v>
+        <v>赵六</v>
       </c>
       <c r="E55" t="str">
-        <v>致命</v>
+        <v>2026-04-25</v>
       </c>
       <c r="F55" t="str">
-        <v>需要与产品确认需求细节，当前需求描述不够清晰。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-03</v>
+        <v>一般</v>
+      </c>
+      <c r="G55" t="str">
+        <v>【暂不处理】经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-08</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Y-BUG-036</v>
+        <v>打开</v>
       </c>
       <c r="B56" t="str">
-        <v>用户注册API接口返回400错误，参数验证失败，需要检查请求参数格式和后端验证逻辑是否匹配</v>
+        <v>Y-BUG-022</v>
       </c>
       <c r="C56" t="str">
-        <v>吴十</v>
+        <v>CI/CD部署失败，Docker镜像构建超时，需要优化构建脚本和依赖下载速度</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-22</v>
+        <v>钱七</v>
       </c>
       <c r="E56" t="str">
-        <v>严重</v>
+        <v>2026-04-24</v>
       </c>
       <c r="F56" t="str">
-        <v>【跟踪中】已经定位到问题根因，是由于异步请求时序问题导致状态不一致。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-07</v>
+        <v>提示</v>
+      </c>
+      <c r="G56" t="str">
+        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B57" t="str">
         <v>Y-BUG-066</v>
       </c>
-      <c r="B57" t="str">
-        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
-      </c>
       <c r="C57" t="str">
-        <v>周九</v>
+        <v>首页数据加载失败，显示空白页面，经检查是接口返回数据格式变更导致JSON解析错误，需要更新数据解析逻辑</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-29</v>
+        <v>陈三</v>
       </c>
       <c r="E57" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="F57" t="str">
         <v>提示</v>
       </c>
-      <c r="F57" t="str">
-        <v>【长期跟踪】需要升级依赖库版本，但可能影响其他模块，需要评估风险。需要升级依赖库版本，但可能影响其他模块，需要评估风险。预计解决时间：2026-05-04</v>
+      <c r="G57" t="str">
+        <v>已修复并发布到测试环境，等待测试验证。已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Y-BUG-033</v>
+        <v>打开</v>
       </c>
       <c r="B58" t="str">
-        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
+        <v>Y-BUG-091</v>
       </c>
       <c r="C58" t="str">
-        <v>刘六</v>
+        <v>Redis缓存失效导致频繁查询数据库，需要检查缓存更新策略和过期时间设置</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-21</v>
+        <v>陈三</v>
       </c>
       <c r="E58" t="str">
-        <v>一般</v>
+        <v>2026-05-01</v>
       </c>
       <c r="F58" t="str">
-        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致</v>
+        <v>严重</v>
+      </c>
+      <c r="G58" t="str">
+        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Y-BUG-060</v>
+        <v>打开</v>
       </c>
       <c r="B59" t="str">
-        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
+        <v>Y-BUG-009</v>
       </c>
       <c r="C59" t="str">
-        <v>赵六</v>
+        <v>报表导出功能模块缺失，用户无法导出Excel格式的统计报表，需要新增导出功能组件和后端接口</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-25</v>
+        <v>吴十</v>
       </c>
       <c r="E59" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="F59" t="str">
         <v>提示</v>
       </c>
-      <c r="F59" t="str">
-        <v>该问题已在测试环境复现，正在编写修复方案</v>
+      <c r="G59" t="str">
+        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Y-BUG-081</v>
+        <v>打开</v>
       </c>
       <c r="B60" t="str">
-        <v>用户列表页面在小屏幕设备上样式错乱，表格列重叠，需要优化响应式布局和媒体查询设置</v>
+        <v>Y-BUG-030</v>
       </c>
       <c r="C60" t="str">
-        <v>王五</v>
+        <v>代码冗余严重，多个组件存在重复逻辑，需要抽取公共组件和工具函数，提高代码复用率</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-26</v>
+        <v>张三</v>
       </c>
       <c r="E60" t="str">
-        <v>一般</v>
+        <v>2026-04-25</v>
       </c>
       <c r="F60" t="str">
-        <v>【deferred】涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-04</v>
+        <v>严重</v>
+      </c>
+      <c r="G60" t="str">
+        <v>【deferred】预计需要2个开发工作日完成修复，包含测试和回归验证。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-07</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Y-BUG-047</v>
+        <v>打开</v>
       </c>
       <c r="B61" t="str">
-        <v>数据库连接池在高并发场景下出现连接耗尽，需要增加连接池最大连接数配置和连接回收机制</v>
+        <v>Y-BUG-077</v>
       </c>
       <c r="C61" t="str">
-        <v>孙八</v>
+        <v>用户列表页面在小屏幕设备上样式错乱，表格列重叠，需要优化响应式布局和媒体查询设置</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-24</v>
+        <v>吴十</v>
       </c>
       <c r="E61" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="F61" t="str">
         <v>提示</v>
       </c>
-      <c r="F61" t="str">
-        <v>【deferred】代码review已通过，等待合并到主分支。代码review已通过，等待合并到主分支。预计解决时间：2026-05-05</v>
+      <c r="G61" t="str">
+        <v>代码review已通过，等待合并到主分支</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Y-BUG-087</v>
+        <v>打开</v>
       </c>
       <c r="B62" t="str">
-        <v>首页数据加载失败，显示空白页面，经检查是接口返回数据格式变更导致JSON解析错误，需要更新数据解析逻辑</v>
+        <v>Y-BUG-047</v>
       </c>
       <c r="C62" t="str">
-        <v>王五</v>
+        <v>数据库连接池在高并发场景下出现连接耗尽，需要增加连接池最大连接数配置和连接回收机制</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-22</v>
+        <v>黄五</v>
       </c>
       <c r="E62" t="str">
-        <v>致命</v>
+        <v>2026-04-29</v>
       </c>
       <c r="F62" t="str">
-        <v>【暂不处理】经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-03</v>
+        <v>严重</v>
+      </c>
+      <c r="G62" t="str">
+        <v>【暂不处理】该问题是已知问题，已列入后续迭代计划。需要升级依赖库版本，但可能影响其他模块，需要评估风险。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Y-BUG-092</v>
+        <v>打开</v>
       </c>
       <c r="B63" t="str">
-        <v>用户列表页面在小屏幕设备上样式错乱，表格列重叠，需要优化响应式布局和媒体查询设置</v>
+        <v>Y-BUG-061</v>
       </c>
       <c r="C63" t="str">
-        <v>郑一</v>
+        <v>用户反馈弹窗关闭按钮位置不合理，用户容易误触，需要优化UI布局和交互体验</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-30</v>
+        <v>王五</v>
       </c>
       <c r="E63" t="str">
-        <v>致命</v>
+        <v>2026-04-25</v>
       </c>
       <c r="F63" t="str">
-        <v>该问题是已知问题，已列入后续迭代计划</v>
+        <v>严重</v>
+      </c>
+      <c r="G63" t="str">
+        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Y-BUG-065</v>
+        <v>打开</v>
       </c>
       <c r="B64" t="str">
-        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
+        <v>Y-BUG-016</v>
       </c>
       <c r="C64" t="str">
-        <v>黄五</v>
+        <v>数据库连接池在高并发场景下出现连接耗尽，需要增加连接池最大连接数配置和连接回收机制</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-26</v>
+        <v>李四</v>
       </c>
       <c r="E64" t="str">
-        <v>提示</v>
+        <v>2026-04-30</v>
       </c>
       <c r="F64" t="str">
-        <v>【跟踪中】预计需要2个开发工作日完成修复，包含测试和回归验证。代码review已通过，等待合并到主分支。预计解决时间：2026-05-03</v>
+        <v>一般</v>
+      </c>
+      <c r="G64" t="str">
+        <v>【暂不处理】已修复并发布到测试环境，等待测试验证。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Y-BUG-097</v>
+        <v>打开</v>
       </c>
       <c r="B65" t="str">
-        <v>Redis缓存失效导致频繁查询数据库，需要检查缓存更新策略和过期时间设置</v>
+        <v>Y-BUG-081</v>
       </c>
       <c r="C65" t="str">
-        <v>杨八</v>
+        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-30</v>
+        <v>林四</v>
       </c>
       <c r="E65" t="str">
-        <v>致命</v>
+        <v>2026-04-29</v>
       </c>
       <c r="F65" t="str">
-        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持</v>
+        <v>一般</v>
+      </c>
+      <c r="G65" t="str">
+        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Y-BUG-099</v>
+        <v>打开</v>
       </c>
       <c r="B66" t="str">
-        <v>CI/CD部署失败，Docker镜像构建超时，需要优化构建脚本和依赖下载速度</v>
+        <v>Y-BUG-005</v>
       </c>
       <c r="C66" t="str">
-        <v>林四</v>
+        <v>iOS端App在iOS 15以下版本兼容性问题，某些功能按钮点击无响应，需要检查事件绑定方式</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-26</v>
+        <v>赵六</v>
       </c>
       <c r="E66" t="str">
-        <v>提示</v>
+        <v>2026-04-29</v>
       </c>
       <c r="F66" t="str">
-        <v>【跟踪中】该问题是已知问题，已列入后续迭代计划。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-08</v>
+        <v>一般</v>
+      </c>
+      <c r="G66" t="str">
+        <v>该问题已在测试环境复现，正在编写修复方案</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Y-BUG-057</v>
+        <v>打开</v>
       </c>
       <c r="B67" t="str">
+        <v>Y-BUG-095</v>
+      </c>
+      <c r="C67" t="str">
         <v>用户密码重置功能存在安全漏洞，重置链接未设置过期时间，可能被恶意利用，需要添加token有效期验证</v>
       </c>
-      <c r="C67" t="str">
-        <v>李四</v>
-      </c>
       <c r="D67" t="str">
-        <v>2026-04-29</v>
+        <v>周九</v>
       </c>
       <c r="E67" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="F67" t="str">
         <v>致命</v>
       </c>
-      <c r="F67" t="str">
-        <v>代码review已通过，等待合并到主分支。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-04</v>
+      <c r="G67" t="str">
+        <v>【deferred】需要与产品确认需求细节，当前需求描述不够清晰。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Y-BUG-088</v>
+        <v>打开</v>
       </c>
       <c r="B68" t="str">
-        <v>数据库连接池在高并发场景下出现连接耗尽，需要增加连接池最大连接数配置和连接回收机制</v>
+        <v>Y-BUG-069</v>
       </c>
       <c r="C68" t="str">
-        <v>黄五</v>
+        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-28</v>
+        <v>杨八</v>
       </c>
       <c r="E68" t="str">
-        <v>一般</v>
+        <v>2026-04-25</v>
       </c>
       <c r="F68" t="str">
-        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-03</v>
+        <v>提示</v>
+      </c>
+      <c r="G68" t="str">
+        <v>已修复并发布到测试环境，等待测试验证。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Y-BUG-095</v>
+        <v>打开</v>
       </c>
       <c r="B69" t="str">
-        <v>用户注册API接口返回400错误，参数验证失败，需要检查请求参数格式和后端验证逻辑是否匹配</v>
+        <v>Y-BUG-028</v>
       </c>
       <c r="C69" t="str">
-        <v>钱七</v>
+        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-22</v>
+        <v>黄五</v>
       </c>
       <c r="E69" t="str">
-        <v>一般</v>
+        <v>2026-05-01</v>
       </c>
       <c r="F69" t="str">
-        <v>【暂不处理】代码review已通过，等待合并到主分支。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-04</v>
+        <v>致命</v>
+      </c>
+      <c r="G69" t="str">
+        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Y-BUG-052</v>
+        <v>打开</v>
       </c>
       <c r="B70" t="str">
-        <v>CI/CD部署失败，Docker镜像构建超时，需要优化构建脚本和依赖下载速度</v>
+        <v>Y-BUG-019</v>
       </c>
       <c r="C70" t="str">
-        <v>王二</v>
+        <v>报表导出功能模块缺失，用户无法导出Excel格式的统计报表，需要新增导出功能组件和后端接口</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-23</v>
+        <v>钱七</v>
       </c>
       <c r="E70" t="str">
-        <v>致命</v>
+        <v>2026-04-29</v>
       </c>
       <c r="F70" t="str">
-        <v>【长期跟踪】该问题是已知问题，已列入后续迭代计划。代码review已通过，等待合并到主分支。预计解决时间：2026-05-09</v>
+        <v>严重</v>
+      </c>
+      <c r="G70" t="str">
+        <v>该问题已在测试环境复现，正在编写修复方案。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Y-BUG-074</v>
+        <v>打开</v>
       </c>
       <c r="B71" t="str">
-        <v>iOS端App在iOS 15以下版本兼容性问题，某些功能按钮点击无响应，需要检查事件绑定方式</v>
+        <v>Y-BUG-011</v>
       </c>
       <c r="C71" t="str">
-        <v>陈三</v>
+        <v>配置文件管理混乱，开发环境和生产环境配置混用，需要建立统一的配置管理方案</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-24</v>
+        <v>钱七</v>
       </c>
       <c r="E71" t="str">
-        <v>一般</v>
+        <v>2026-04-25</v>
       </c>
       <c r="F71" t="str">
-        <v>该问题已在测试环境复现，正在编写修复方案。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-04</v>
+        <v>严重</v>
+      </c>
+      <c r="G71" t="str">
+        <v>已修复并发布到测试环境，等待测试验证。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Y-BUG-089</v>
+        <v>打开</v>
       </c>
       <c r="B72" t="str">
-        <v>iOS端App在iOS 15以下版本兼容性问题，某些功能按钮点击无响应，需要检查事件绑定方式</v>
+        <v>Y-BUG-049</v>
       </c>
       <c r="C72" t="str">
-        <v>孙八</v>
+        <v>用户列表页面在小屏幕设备上样式错乱，表格列重叠，需要优化响应式布局和媒体查询设置</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-29</v>
+        <v>陈三</v>
       </c>
       <c r="E72" t="str">
-        <v>严重</v>
+        <v>2026-04-30</v>
       </c>
       <c r="F72" t="str">
-        <v>该问题已在测试环境复现，正在编写修复方案。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-04</v>
+        <v>致命</v>
+      </c>
+      <c r="G72" t="str">
+        <v>该问题是已知问题，已列入后续迭代计划</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Y-BUG-093</v>
+        <v>打开</v>
       </c>
       <c r="B73" t="str">
-        <v>用户注册API接口返回400错误，参数验证失败，需要检查请求参数格式和后端验证逻辑是否匹配</v>
+        <v>Y-BUG-088</v>
       </c>
       <c r="C73" t="str">
-        <v>陈三</v>
+        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-23</v>
+        <v>孙八</v>
       </c>
       <c r="E73" t="str">
-        <v>严重</v>
+        <v>2026-04-26</v>
       </c>
       <c r="F73" t="str">
-        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-05</v>
+        <v>提示</v>
+      </c>
+      <c r="G73" t="str">
+        <v>【暂不处理】需要与产品确认需求细节，当前需求描述不够清晰。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-06</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Y-BUG-064</v>
+        <v>打开</v>
       </c>
       <c r="B74" t="str">
-        <v>代码冗余严重，多个组件存在重复逻辑，需要抽取公共组件和工具函数，提高代码复用率</v>
+        <v>Y-BUG-017</v>
       </c>
       <c r="C74" t="str">
-        <v>王五</v>
+        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-26</v>
+        <v>陈三</v>
       </c>
       <c r="E74" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="F74" t="str">
         <v>严重</v>
       </c>
-      <c r="F74" t="str">
-        <v>代码review已通过，等待合并到主分支</v>
+      <c r="G74" t="str">
+        <v>经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Y-BUG-100</v>
+        <v>打开</v>
       </c>
       <c r="B75" t="str">
-        <v>订单状态流转逻辑错误，已取消的订单仍能继续支付，需要修复状态机转换规则</v>
+        <v>Y-BUG-013</v>
       </c>
       <c r="C75" t="str">
-        <v>郑一</v>
+        <v>代码冗余严重，多个组件存在重复逻辑，需要抽取公共组件和工具函数，提高代码复用率</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-21</v>
+        <v>杨八</v>
       </c>
       <c r="E75" t="str">
-        <v>严重</v>
+        <v>2026-05-01</v>
       </c>
       <c r="F75" t="str">
-        <v>该问题是已知问题，已列入后续迭代计划</v>
+        <v>提示</v>
+      </c>
+      <c r="G75" t="str">
+        <v>经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Y-BUG-076</v>
+        <v>打开</v>
       </c>
       <c r="B76" t="str">
-        <v>用户权限验证逻辑存在漏洞，普通用户可以访问管理员页面，需要加强路由守卫和权限检查</v>
+        <v>Y-BUG-039</v>
       </c>
       <c r="C76" t="str">
-        <v>陈七</v>
+        <v>用户反馈弹窗关闭按钮位置不合理，用户容易误触，需要优化UI布局和交互体验</v>
       </c>
       <c r="D76" t="str">
+        <v>刘六</v>
+      </c>
+      <c r="E76" t="str">
         <v>2026-04-29</v>
       </c>
-      <c r="E76" t="str">
+      <c r="F76" t="str">
         <v>严重</v>
       </c>
-      <c r="F76" t="str">
-        <v>该问题是已知问题，已列入后续迭代计划。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-04</v>
+      <c r="G76" t="str">
+        <v>【跟踪中】已修复并发布到测试环境，等待测试验证。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Y-BUG-080</v>
+        <v>打开</v>
       </c>
       <c r="B77" t="str">
-        <v>用户权限验证逻辑存在漏洞，普通用户可以访问管理员页面，需要加强路由守卫和权限检查</v>
+        <v>Y-BUG-100</v>
       </c>
       <c r="C77" t="str">
-        <v>刘六</v>
+        <v>用户密码重置功能存在安全漏洞，重置链接未设置过期时间，可能被恶意利用，需要添加token有效期验证</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-01</v>
+        <v>陈三</v>
       </c>
       <c r="E77" t="str">
-        <v>一般</v>
+        <v>2026-04-25</v>
       </c>
       <c r="F77" t="str">
-        <v>经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-03</v>
+        <v>严重</v>
+      </c>
+      <c r="G77" t="str">
+        <v>预计需要2个开发工作日完成修复，包含测试和回归验证</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Y-BUG-051</v>
+        <v>打开</v>
       </c>
       <c r="B78" t="str">
-        <v>代码冗余严重，多个组件存在重复逻辑，需要抽取公共组件和工具函数，提高代码复用率</v>
+        <v>Y-BUG-097</v>
       </c>
       <c r="C78" t="str">
-        <v>黄五</v>
+        <v>用户反馈弹窗关闭按钮位置不合理，用户容易误触，需要优化UI布局和交互体验</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-27</v>
+        <v>陈三</v>
       </c>
       <c r="E78" t="str">
-        <v>严重</v>
+        <v>2026-04-29</v>
       </c>
       <c r="F78" t="str">
-        <v>代码review已通过，等待合并到主分支。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-05</v>
+        <v>致命</v>
+      </c>
+      <c r="G78" t="str">
+        <v>经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Y-BUG-096</v>
+        <v>打开</v>
       </c>
       <c r="B79" t="str">
+        <v>Y-BUG-051</v>
+      </c>
+      <c r="C79" t="str">
         <v>用户列表页面在小屏幕设备上样式错乱，表格列重叠，需要优化响应式布局和媒体查询设置</v>
       </c>
-      <c r="C79" t="str">
-        <v>王二</v>
-      </c>
       <c r="D79" t="str">
-        <v>2026-05-01</v>
+        <v>林四</v>
       </c>
       <c r="E79" t="str">
-        <v>致命</v>
+        <v>2026-04-29</v>
       </c>
       <c r="F79" t="str">
-        <v>【pending】预计需要2个开发工作日完成修复，包含测试和回归验证。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-04</v>
+        <v>提示</v>
+      </c>
+      <c r="G79" t="str">
+        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Y-BUG-055</v>
+        <v>打开</v>
       </c>
       <c r="B80" t="str">
-        <v>测试用例覆盖率不足60%，核心功能缺少单元测试，需要补充测试用例确保代码质量</v>
+        <v>Y-BUG-037</v>
       </c>
       <c r="C80" t="str">
-        <v>黄五</v>
+        <v>用户注册API接口返回400错误，参数验证失败，需要检查请求参数格式和后端验证逻辑是否匹配</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-21</v>
+        <v>杨八</v>
       </c>
       <c r="E80" t="str">
-        <v>提示</v>
+        <v>2026-04-22</v>
       </c>
       <c r="F80" t="str">
-        <v>该问题是已知问题，已列入后续迭代计划</v>
+        <v>严重</v>
+      </c>
+      <c r="G80" t="str">
+        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Y-BUG-062</v>
+        <v>打开</v>
       </c>
       <c r="B81" t="str">
-        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
+        <v>Y-BUG-057</v>
       </c>
       <c r="C81" t="str">
-        <v>杨八</v>
+        <v>iOS端App在iOS 15以下版本兼容性问题，某些功能按钮点击无响应，需要检查事件绑定方式</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-22</v>
+        <v>刘六</v>
       </c>
       <c r="E81" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="F81" t="str">
         <v>严重</v>
       </c>
-      <c r="F81" t="str">
-        <v>【跟踪中】已修复并发布到测试环境，等待测试验证。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-04</v>
+      <c r="G81" t="str">
+        <v>【暂不处理】涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B82" t="str">
         <v>T-BUG-001</v>
       </c>
-      <c r="B82" t="str">
-        <v>数据库连接池在高并发场景下出现连接耗尽，需要增加连接池最大连接数配置和连接回收机制</v>
-      </c>
       <c r="C82" t="str">
-        <v>张三</v>
+        <v>用户反馈弹窗关闭按钮位置不合理，用户容易误触，需要优化UI布局和交互体验</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-24</v>
+        <v>王五</v>
       </c>
       <c r="E82" t="str">
-        <v>严重</v>
+        <v>2026-04-26</v>
       </c>
       <c r="F82" t="str">
-        <v>该问题是已知问题，已列入后续迭代计划</v>
+        <v>一般</v>
+      </c>
+      <c r="G82" t="str">
+        <v>需要与产品确认需求细节，当前需求描述不够清晰。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B83" t="str">
         <v>T-BUG-002</v>
       </c>
-      <c r="B83" t="str">
-        <v>首页加载性能问题严重，首屏渲染时间超过5秒，需要优化图片压缩、开启懒加载和代码分割</v>
-      </c>
       <c r="C83" t="str">
-        <v>林四</v>
+        <v>iOS端App在iOS 15以下版本兼容性问题，某些功能按钮点击无响应，需要检查事件绑定方式</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-27</v>
+        <v>张三</v>
       </c>
       <c r="E83" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="F83" t="str">
         <v>致命</v>
       </c>
-      <c r="F83" t="str">
-        <v>【长期跟踪】预计需要2个开发工作日完成修复，包含测试和回归验证。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-07</v>
+      <c r="G83" t="str">
+        <v>【长期跟踪】需要升级依赖库版本，但可能影响其他模块，需要评估风险。预计需要2个开发工作日完成修复，包含测试和回归验证。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B84" t="str">
         <v>T-BUG-003</v>
       </c>
-      <c r="B84" t="str">
-        <v>用户反馈弹窗关闭按钮位置不合理，用户容易误触，需要优化UI布局和交互体验</v>
-      </c>
       <c r="C84" t="str">
-        <v>陈七</v>
+        <v>订单状态流转逻辑错误，已取消的订单仍能继续支付，需要修复状态机转换规则</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-29</v>
+        <v>周九</v>
       </c>
       <c r="E84" t="str">
-        <v>一般</v>
+        <v>2026-04-25</v>
       </c>
       <c r="F84" t="str">
-        <v>该问题已在测试环境复现，正在编写修复方案</v>
+        <v>提示</v>
+      </c>
+      <c r="G84" t="str">
+        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B85" t="str">
         <v>T-BUG-004</v>
       </c>
-      <c r="B85" t="str">
-        <v>代码冗余严重，多个组件存在重复逻辑，需要抽取公共组件和工具函数，提高代码复用率</v>
-      </c>
       <c r="C85" t="str">
-        <v>钱七</v>
+        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
       </c>
       <c r="D85" t="str">
+        <v>陈三</v>
+      </c>
+      <c r="E85" t="str">
         <v>2026-05-01</v>
       </c>
-      <c r="E85" t="str">
-        <v>提示</v>
-      </c>
       <c r="F85" t="str">
-        <v>需要与产品确认需求细节，当前需求描述不够清晰</v>
+        <v>一般</v>
+      </c>
+      <c r="G85" t="str">
+        <v>【暂不处理】代码review已通过，等待合并到主分支。已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计解决时间：2026-05-07</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B86" t="str">
         <v>T-BUG-005</v>
       </c>
-      <c r="B86" t="str">
-        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
-      </c>
       <c r="C86" t="str">
-        <v>王五</v>
+        <v>订单状态流转逻辑错误，已取消的订单仍能继续支付，需要修复状态机转换规则</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-01</v>
+        <v>李四</v>
       </c>
       <c r="E86" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="F86" t="str">
         <v>提示</v>
       </c>
-      <c r="F86" t="str">
-        <v>预计需要2个开发工作日完成修复，包含测试和回归验证。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-04</v>
+      <c r="G86" t="str">
+        <v>已修复并发布到测试环境，等待测试验证</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B87" t="str">
         <v>T-BUG-006</v>
       </c>
-      <c r="B87" t="str">
-        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
-      </c>
       <c r="C87" t="str">
-        <v>张三</v>
+        <v>用户权限验证逻辑存在漏洞，普通用户可以访问管理员页面，需要加强路由守卫和权限检查</v>
       </c>
       <c r="D87" t="str">
+        <v>王五</v>
+      </c>
+      <c r="E87" t="str">
         <v>2026-04-26</v>
       </c>
-      <c r="E87" t="str">
-        <v>一般</v>
-      </c>
       <c r="F87" t="str">
-        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-04</v>
+        <v>提示</v>
+      </c>
+      <c r="G87" t="str">
+        <v>【pending】已经定位到问题根因，是由于异步请求时序问题导致状态不一致。代码review已通过，等待合并到主分支。预计解决时间：2026-05-07</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B88" t="str">
         <v>T-BUG-007</v>
       </c>
-      <c r="B88" t="str">
-        <v>支付功能在移动端提交订单时出现网络超时错误，经排查发现是API请求超时时间设置过短，需要调整axios的timeout配置</v>
-      </c>
       <c r="C88" t="str">
-        <v>张三</v>
+        <v>订单状态流转逻辑错误，已取消的订单仍能继续支付，需要修复状态机转换规则</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-24</v>
+        <v>陈七</v>
       </c>
       <c r="E88" t="str">
-        <v>严重</v>
+        <v>2026-04-22</v>
       </c>
       <c r="F88" t="str">
-        <v>已修复并发布到测试环境，等待测试验证。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-05</v>
+        <v>提示</v>
+      </c>
+      <c r="G88" t="str">
+        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B89" t="str">
         <v>T-BUG-008</v>
       </c>
-      <c r="B89" t="str">
-        <v>iOS端App在iOS 15以下版本兼容性问题，某些功能按钮点击无响应，需要检查事件绑定方式</v>
-      </c>
       <c r="C89" t="str">
-        <v>陈七</v>
+        <v>用户注册API接口返回400错误，参数验证失败，需要检查请求参数格式和后端验证逻辑是否匹配</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-26</v>
+        <v>张三</v>
       </c>
       <c r="E89" t="str">
-        <v>致命</v>
+        <v>2026-04-23</v>
       </c>
       <c r="F89" t="str">
-        <v>已修复并发布到测试环境，等待测试验证。代码review已通过，等待合并到主分支。预计解决时间：2026-05-05</v>
+        <v>一般</v>
+      </c>
+      <c r="G89" t="str">
+        <v>该问题是已知问题，已列入后续迭代计划</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B90" t="str">
         <v>T-BUG-009</v>
       </c>
-      <c r="B90" t="str">
-        <v>配置文件管理混乱，开发环境和生产环境配置混用，需要建立统一的配置管理方案</v>
-      </c>
       <c r="C90" t="str">
-        <v>孙八</v>
+        <v>Redis缓存失效导致频繁查询数据库，需要检查缓存更新策略和过期时间设置</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-23</v>
+        <v>陈三</v>
       </c>
       <c r="E90" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="F90" t="str">
         <v>一般</v>
       </c>
-      <c r="F90" t="str">
-        <v>该问题是已知问题，已列入后续迭代计划。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-03</v>
+      <c r="G90" t="str">
+        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B91" t="str">
         <v>T-BUG-010</v>
       </c>
-      <c r="B91" t="str">
-        <v>首页加载性能问题严重，首屏渲染时间超过5秒，需要优化图片压缩、开启懒加载和代码分割</v>
-      </c>
       <c r="C91" t="str">
-        <v>张三</v>
+        <v>iOS端App在iOS 15以下版本兼容性问题，某些功能按钮点击无响应，需要检查事件绑定方式</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-24</v>
+        <v>杨八</v>
       </c>
       <c r="E91" t="str">
-        <v>提示</v>
+        <v>2026-04-29</v>
       </c>
       <c r="F91" t="str">
-        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持</v>
+        <v>一般</v>
+      </c>
+      <c r="G91" t="str">
+        <v>该问题已在测试环境复现，正在编写修复方案</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B92" t="str">
         <v>T-BUG-011</v>
       </c>
-      <c r="B92" t="str">
-        <v>支付功能在移动端提交订单时出现网络超时错误，经排查发现是API请求超时时间设置过短，需要调整axios的timeout配置</v>
-      </c>
       <c r="C92" t="str">
-        <v>张三</v>
+        <v>首页数据加载失败，显示空白页面，经检查是接口返回数据格式变更导致JSON解析错误，需要更新数据解析逻辑</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-25</v>
+        <v>陈三</v>
       </c>
       <c r="E92" t="str">
-        <v>严重</v>
+        <v>2026-05-01</v>
       </c>
       <c r="F92" t="str">
-        <v>经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查</v>
+        <v>致命</v>
+      </c>
+      <c r="G92" t="str">
+        <v>需要与产品确认需求细节，当前需求描述不够清晰。预计需要2个开发工作日完成修复，包含测试和回归验证。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B93" t="str">
         <v>T-BUG-012</v>
       </c>
-      <c r="B93" t="str">
-        <v>测试用例覆盖率不足60%，核心功能缺少单元测试，需要补充测试用例确保代码质量</v>
-      </c>
       <c r="C93" t="str">
-        <v>陈七</v>
+        <v>iOS端App在iOS 15以下版本兼容性问题，某些功能按钮点击无响应，需要检查事件绑定方式</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-22</v>
+        <v>郑一</v>
       </c>
       <c r="E93" t="str">
-        <v>提示</v>
+        <v>2026-04-28</v>
       </c>
       <c r="F93" t="str">
-        <v>代码review已通过，等待合并到主分支。代码review已通过，等待合并到主分支。预计解决时间：2026-05-03</v>
+        <v>严重</v>
+      </c>
+      <c r="G93" t="str">
+        <v>已修复并发布到测试环境，等待测试验证</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B94" t="str">
         <v>T-BUG-013</v>
       </c>
-      <c r="B94" t="str">
-        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
-      </c>
       <c r="C94" t="str">
-        <v>周九</v>
+        <v>订单状态流转逻辑错误，已取消的订单仍能继续支付，需要修复状态机转换规则</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-29</v>
+        <v>陈三</v>
       </c>
       <c r="E94" t="str">
-        <v>一般</v>
+        <v>2026-04-30</v>
       </c>
       <c r="F94" t="str">
-        <v>【暂不处理】已修复并发布到测试环境，等待测试验证。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-03</v>
+        <v>提示</v>
+      </c>
+      <c r="G94" t="str">
+        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B95" t="str">
         <v>T-BUG-014</v>
       </c>
-      <c r="B95" t="str">
-        <v>配置文件管理混乱，开发环境和生产环境配置混用，需要建立统一的配置管理方案</v>
-      </c>
       <c r="C95" t="str">
-        <v>张三</v>
+        <v>数据库连接池在高并发场景下出现连接耗尽，需要增加连接池最大连接数配置和连接回收机制</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-24</v>
+        <v>王二</v>
       </c>
       <c r="E95" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="F95" t="str">
         <v>致命</v>
       </c>
-      <c r="F95" t="str">
-        <v>已修复并发布到测试环境，等待测试验证</v>
+      <c r="G95" t="str">
+        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致。需要升级依赖库版本，但可能影响其他模块，需要评估风险。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B96" t="str">
         <v>T-BUG-015</v>
       </c>
-      <c r="B96" t="str">
-        <v>测试用例覆盖率不足60%，核心功能缺少单元测试，需要补充测试用例确保代码质量</v>
-      </c>
       <c r="C96" t="str">
-        <v>陈三</v>
+        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-25</v>
+        <v>钱七</v>
       </c>
       <c r="E96" t="str">
-        <v>致命</v>
+        <v>2026-04-22</v>
       </c>
       <c r="F96" t="str">
-        <v>预计需要2个开发工作日完成修复，包含测试和回归验证。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-05</v>
+        <v>提示</v>
+      </c>
+      <c r="G96" t="str">
+        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B97" t="str">
         <v>T-BUG-016</v>
       </c>
-      <c r="B97" t="str">
-        <v>用户权限验证逻辑存在漏洞，普通用户可以访问管理员页面，需要加强路由守卫和权限检查</v>
-      </c>
       <c r="C97" t="str">
-        <v>张三</v>
+        <v>异常处理缺失导致错误信息直接暴露给用户，可能泄露系统敏感信息，需要统一错误处理和日志记录</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-28</v>
+        <v>李四</v>
       </c>
       <c r="E97" t="str">
-        <v>提示</v>
+        <v>2026-04-30</v>
       </c>
       <c r="F97" t="str">
-        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持</v>
+        <v>一般</v>
+      </c>
+      <c r="G97" t="str">
+        <v>【deferred】已修复并发布到测试环境，等待测试验证。已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计解决时间：2026-05-07</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B98" t="str">
         <v>T-BUG-017</v>
       </c>
-      <c r="B98" t="str">
-        <v>订单状态流转逻辑错误，已取消的订单仍能继续支付，需要修复状态机转换规则</v>
-      </c>
       <c r="C98" t="str">
-        <v>孙八</v>
+        <v>测试用例覆盖率不足60%，核心功能缺少单元测试，需要补充测试用例确保代码质量</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-27</v>
+        <v>陈七</v>
       </c>
       <c r="E98" t="str">
-        <v>致命</v>
+        <v>2026-04-23</v>
       </c>
       <c r="F98" t="str">
-        <v>该问题已在测试环境复现，正在编写修复方案。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-04</v>
+        <v>严重</v>
+      </c>
+      <c r="G98" t="str">
+        <v>预计需要2个开发工作日完成修复，包含测试和回归验证</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B99" t="str">
         <v>T-BUG-018</v>
       </c>
-      <c r="B99" t="str">
-        <v>支付功能在移动端提交订单时出现网络超时错误，经排查发现是API请求超时时间设置过短，需要调整axios的timeout配置</v>
-      </c>
       <c r="C99" t="str">
-        <v>王二</v>
+        <v>用户注册API接口返回400错误，参数验证失败，需要检查请求参数格式和后端验证逻辑是否匹配</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-25</v>
+        <v>陈七</v>
       </c>
       <c r="E99" t="str">
-        <v>致命</v>
+        <v>2026-05-02</v>
       </c>
       <c r="F99" t="str">
-        <v>已修复并发布到测试环境，等待测试验证</v>
+        <v>一般</v>
+      </c>
+      <c r="G99" t="str">
+        <v>预计需要2个开发工作日完成修复，包含测试和回归验证。代码review已通过，等待合并到主分支。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B100" t="str">
         <v>T-BUG-019</v>
       </c>
-      <c r="B100" t="str">
-        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
-      </c>
       <c r="C100" t="str">
-        <v>杨八</v>
+        <v>用户密码重置功能存在安全漏洞，重置链接未设置过期时间，可能被恶意利用，需要添加token有效期验证</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-25</v>
+        <v>郑一</v>
       </c>
       <c r="E100" t="str">
-        <v>提示</v>
+        <v>2026-04-22</v>
       </c>
       <c r="F100" t="str">
-        <v>【暂不处理】预计需要2个开发工作日完成修复，包含测试和回归验证。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-09</v>
+        <v>致命</v>
+      </c>
+      <c r="G100" t="str">
+        <v>【跟踪中】需要与产品确认需求细节，当前需求描述不够清晰。代码review已通过，等待合并到主分支。预计解决时间：2026-05-09</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B101" t="str">
         <v>T-BUG-020</v>
       </c>
-      <c r="B101" t="str">
-        <v>首页数据加载失败，显示空白页面，经检查是接口返回数据格式变更导致JSON解析错误，需要更新数据解析逻辑</v>
-      </c>
       <c r="C101" t="str">
-        <v>吴十</v>
+        <v>代码冗余严重，多个组件存在重复逻辑，需要抽取公共组件和工具函数，提高代码复用率</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-30</v>
+        <v>杨八</v>
       </c>
       <c r="E101" t="str">
-        <v>提示</v>
+        <v>2026-04-23</v>
       </c>
       <c r="F101" t="str">
-        <v>【deferred】经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-09</v>
+        <v>严重</v>
+      </c>
+      <c r="G101" t="str">
+        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险。代码review已通过，等待合并到主分支。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B102" t="str">
         <v>T-BUG-021</v>
       </c>
-      <c r="B102" t="str">
-        <v>支付功能在移动端提交订单时出现网络超时错误，经排查发现是API请求超时时间设置过短，需要调整axios的timeout配置</v>
-      </c>
       <c r="C102" t="str">
-        <v>王二</v>
+        <v>Redis缓存失效导致频繁查询数据库，需要检查缓存更新策略和过期时间设置</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-04-23</v>
+        <v>周九</v>
       </c>
       <c r="E102" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="F102" t="str">
         <v>一般</v>
       </c>
-      <c r="F102" t="str">
-        <v>经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-03</v>
+      <c r="G102" t="str">
+        <v>该问题是已知问题，已列入后续迭代计划</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B103" t="str">
         <v>T-BUG-022</v>
       </c>
-      <c r="B103" t="str">
-        <v>数据库连接池在高并发场景下出现连接耗尽，需要增加连接池最大连接数配置和连接回收机制</v>
-      </c>
       <c r="C103" t="str">
-        <v>刘六</v>
+        <v>iOS端App在iOS 15以下版本兼容性问题，某些功能按钮点击无响应，需要检查事件绑定方式</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-04-26</v>
+        <v>王二</v>
       </c>
       <c r="E103" t="str">
-        <v>严重</v>
+        <v>2026-04-23</v>
       </c>
       <c r="F103" t="str">
-        <v>【pending】已经定位到问题根因，是由于异步请求时序问题导致状态不一致。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-04</v>
+        <v>致命</v>
+      </c>
+      <c r="G103" t="str">
+        <v>【长期跟踪】已修复并发布到测试环境，等待测试验证。该问题是已知问题，已列入后续迭代计划。预计解决时间：2026-05-09</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B104" t="str">
         <v>T-BUG-023</v>
       </c>
-      <c r="B104" t="str">
-        <v>支付功能在移动端提交订单时出现网络超时错误，经排查发现是API请求超时时间设置过短，需要调整axios的timeout配置</v>
-      </c>
       <c r="C104" t="str">
-        <v>张三</v>
+        <v>用户密码重置功能存在安全漏洞，重置链接未设置过期时间，可能被恶意利用，需要添加token有效期验证</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-04-30</v>
+        <v>黄五</v>
       </c>
       <c r="E104" t="str">
-        <v>致命</v>
+        <v>2026-04-26</v>
       </c>
       <c r="F104" t="str">
-        <v>经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查</v>
+        <v>严重</v>
+      </c>
+      <c r="G104" t="str">
+        <v>预计需要2个开发工作日完成修复，包含测试和回归验证。预计需要2个开发工作日完成修复，包含测试和回归验证。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B105" t="str">
         <v>T-BUG-024</v>
       </c>
-      <c r="B105" t="str">
-        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
-      </c>
       <c r="C105" t="str">
-        <v>杨八</v>
+        <v>配置文件管理混乱，开发环境和生产环境配置混用，需要建立统一的配置管理方案</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-04-26</v>
+        <v>张三</v>
       </c>
       <c r="E105" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="F105" t="str">
         <v>一般</v>
       </c>
-      <c r="F105" t="str">
-        <v>【deferred】预计需要2个开发工作日完成修复，包含测试和回归验证。需要升级依赖库版本，但可能影响其他模块，需要评估风险。预计解决时间：2026-05-04</v>
+      <c r="G105" t="str">
+        <v>【deferred】该问题已在测试环境复现，正在编写修复方案。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B106" t="str">
         <v>T-BUG-025</v>
       </c>
-      <c r="B106" t="str">
-        <v>用户权限验证逻辑存在漏洞，普通用户可以访问管理员页面，需要加强路由守卫和权限检查</v>
-      </c>
       <c r="C106" t="str">
-        <v>黄五</v>
+        <v>iOS端App在iOS 15以下版本兼容性问题，某些功能按钮点击无响应，需要检查事件绑定方式</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-04-30</v>
+        <v>周九</v>
       </c>
       <c r="E106" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="F106" t="str">
         <v>严重</v>
       </c>
-      <c r="F106" t="str">
-        <v>【长期跟踪】预计需要2个开发工作日完成修复，包含测试和回归验证。预计需要2个开发工作日完成修复，包含测试和回归验证。预计解决时间：2026-05-07</v>
+      <c r="G106" t="str">
+        <v>已修复并发布到测试环境，等待测试验证。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-03</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B107" t="str">
         <v>T-BUG-026</v>
       </c>
-      <c r="B107" t="str">
-        <v>Redis缓存失效导致频繁查询数据库，需要检查缓存更新策略和过期时间设置</v>
-      </c>
       <c r="C107" t="str">
-        <v>林四</v>
+        <v>代码冗余严重，多个组件存在重复逻辑，需要抽取公共组件和工具函数，提高代码复用率</v>
       </c>
       <c r="D107" t="str">
+        <v>周九</v>
+      </c>
+      <c r="E107" t="str">
         <v>2026-04-30</v>
       </c>
-      <c r="E107" t="str">
-        <v>严重</v>
-      </c>
       <c r="F107" t="str">
-        <v>代码review已通过，等待合并到主分支</v>
+        <v>致命</v>
+      </c>
+      <c r="G107" t="str">
+        <v>【长期跟踪】代码review已通过，等待合并到主分支。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-06</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B108" t="str">
         <v>T-BUG-027</v>
       </c>
-      <c r="B108" t="str">
-        <v>用户密码重置功能存在安全漏洞，重置链接未设置过期时间，可能被恶意利用，需要添加token有效期验证</v>
-      </c>
       <c r="C108" t="str">
-        <v>郑一</v>
+        <v>支付功能在移动端提交订单时出现网络超时错误，经排查发现是API请求超时时间设置过短，需要调整axios的timeout配置</v>
       </c>
       <c r="D108" t="str">
+        <v>黄五</v>
+      </c>
+      <c r="E108" t="str">
         <v>2026-04-25</v>
       </c>
-      <c r="E108" t="str">
-        <v>一般</v>
-      </c>
       <c r="F108" t="str">
-        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致。已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计解决时间：2026-05-03</v>
+        <v>提示</v>
+      </c>
+      <c r="G108" t="str">
+        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B109" t="str">
         <v>T-BUG-028</v>
       </c>
-      <c r="B109" t="str">
-        <v>iOS端App在iOS 15以下版本兼容性问题，某些功能按钮点击无响应，需要检查事件绑定方式</v>
-      </c>
       <c r="C109" t="str">
-        <v>杨八</v>
+        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
       </c>
       <c r="D109" t="str">
+        <v>黄五</v>
+      </c>
+      <c r="E109" t="str">
         <v>2026-04-28</v>
       </c>
-      <c r="E109" t="str">
-        <v>严重</v>
-      </c>
       <c r="F109" t="str">
-        <v>该问题是已知问题，已列入后续迭代计划</v>
+        <v>一般</v>
+      </c>
+      <c r="G109" t="str">
+        <v>【deferred】涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-06</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B110" t="str">
         <v>T-BUG-029</v>
       </c>
-      <c r="B110" t="str">
-        <v>首页加载性能问题严重，首屏渲染时间超过5秒，需要优化图片压缩、开启懒加载和代码分割</v>
-      </c>
       <c r="C110" t="str">
-        <v>陈三</v>
+        <v>CI/CD部署失败，Docker镜像构建超时，需要优化构建脚本和依赖下载速度</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-05-01</v>
+        <v>黄五</v>
       </c>
       <c r="E110" t="str">
-        <v>提示</v>
+        <v>2026-05-02</v>
       </c>
       <c r="F110" t="str">
-        <v>【deferred】该问题已在测试环境复现，正在编写修复方案。需要升级依赖库版本，但可能影响其他模块，需要评估风险。预计解决时间：2026-05-06</v>
+        <v>一般</v>
+      </c>
+      <c r="G110" t="str">
+        <v>【pending】该问题是已知问题，已列入后续迭代计划。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-06</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B111" t="str">
         <v>T-BUG-030</v>
       </c>
-      <c r="B111" t="str">
-        <v>用户密码重置功能存在安全漏洞，重置链接未设置过期时间，可能被恶意利用，需要添加token有效期验证</v>
-      </c>
       <c r="C111" t="str">
-        <v>陈七</v>
+        <v>订单状态流转逻辑错误，已取消的订单仍能继续支付，需要修复状态机转换规则</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-04-22</v>
+        <v>王二</v>
       </c>
       <c r="E111" t="str">
-        <v>一般</v>
+        <v>2026-04-27</v>
       </c>
       <c r="F111" t="str">
-        <v>【暂不处理】预计需要2个开发工作日完成修复，包含测试和回归验证。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-03</v>
+        <v>严重</v>
+      </c>
+      <c r="G111" t="str">
+        <v>经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B112" t="str">
         <v>T-BUG-031</v>
       </c>
-      <c r="B112" t="str">
+      <c r="C112" t="str">
         <v>用户列表页面在小屏幕设备上样式错乱，表格列重叠，需要优化响应式布局和媒体查询设置</v>
       </c>
-      <c r="C112" t="str">
-        <v>钱七</v>
-      </c>
       <c r="D112" t="str">
-        <v>2026-04-26</v>
+        <v>李四</v>
       </c>
       <c r="E112" t="str">
-        <v>严重</v>
+        <v>2026-04-27</v>
       </c>
       <c r="F112" t="str">
-        <v>预计需要2个开发工作日完成修复，包含测试和回归验证</v>
+        <v>一般</v>
+      </c>
+      <c r="G112" t="str">
+        <v>已修复并发布到测试环境，等待测试验证。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B113" t="str">
         <v>T-BUG-032</v>
       </c>
-      <c r="B113" t="str">
-        <v>首页加载性能问题严重，首屏渲染时间超过5秒，需要优化图片压缩、开启懒加载和代码分割</v>
-      </c>
       <c r="C113" t="str">
-        <v>刘六</v>
+        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-04-28</v>
+        <v>吴十</v>
       </c>
       <c r="E113" t="str">
-        <v>提示</v>
+        <v>2026-04-30</v>
       </c>
       <c r="F113" t="str">
-        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险</v>
+        <v>致命</v>
+      </c>
+      <c r="G113" t="str">
+        <v>代码review已通过，等待合并到主分支。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B114" t="str">
         <v>T-BUG-033</v>
       </c>
-      <c r="B114" t="str">
-        <v>代码冗余严重，多个组件存在重复逻辑，需要抽取公共组件和工具函数，提高代码复用率</v>
-      </c>
       <c r="C114" t="str">
-        <v>刘六</v>
+        <v>iOS端App在iOS 15以下版本兼容性问题，某些功能按钮点击无响应，需要检查事件绑定方式</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-04-22</v>
+        <v>李四</v>
       </c>
       <c r="E114" t="str">
-        <v>一般</v>
+        <v>2026-04-23</v>
       </c>
       <c r="F114" t="str">
-        <v>已修复并发布到测试环境，等待测试验证。经初步分析，问题可能出在第3行的变量未初始化，需要添加默认值检查。预计解决时间：2026-05-05</v>
+        <v>严重</v>
+      </c>
+      <c r="G114" t="str">
+        <v>【长期跟踪】需要与产品确认需求细节，当前需求描述不够清晰。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B115" t="str">
         <v>T-BUG-034</v>
       </c>
-      <c r="B115" t="str">
-        <v>订单状态流转逻辑错误，已取消的订单仍能继续支付，需要修复状态机转换规则</v>
-      </c>
       <c r="C115" t="str">
-        <v>林四</v>
+        <v>用户列表页面在小屏幕设备上样式错乱，表格列重叠，需要优化响应式布局和媒体查询设置</v>
       </c>
       <c r="D115" t="str">
+        <v>吴十</v>
+      </c>
+      <c r="E115" t="str">
         <v>2026-04-29</v>
       </c>
-      <c r="E115" t="str">
-        <v>一般</v>
-      </c>
       <c r="F115" t="str">
-        <v>代码review已通过，等待合并到主分支。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-03</v>
+        <v>严重</v>
+      </c>
+      <c r="G115" t="str">
+        <v>预计需要2个开发工作日完成修复，包含测试和回归验证。预计需要2个开发工作日完成修复，包含测试和回归验证。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B116" t="str">
         <v>T-BUG-035</v>
       </c>
-      <c r="B116" t="str">
-        <v>用户注册API接口返回400错误，参数验证失败，需要检查请求参数格式和后端验证逻辑是否匹配</v>
-      </c>
       <c r="C116" t="str">
-        <v>陈七</v>
+        <v>首页加载性能问题严重，首屏渲染时间超过5秒，需要优化图片压缩、开启懒加载和代码分割</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-04-27</v>
+        <v>杨八</v>
       </c>
       <c r="E116" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="F116" t="str">
         <v>提示</v>
       </c>
-      <c r="F116" t="str">
-        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险</v>
+      <c r="G116" t="str">
+        <v>已经定位到问题根因，是由于异步请求时序问题导致状态不一致。需要与产品确认需求细节，当前需求描述不够清晰。预计解决时间：2026-05-05</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B117" t="str">
         <v>T-BUG-036</v>
       </c>
-      <c r="B117" t="str">
-        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
-      </c>
       <c r="C117" t="str">
-        <v>刘六</v>
+        <v>用户密码重置功能存在安全漏洞，重置链接未设置过期时间，可能被恶意利用，需要添加token有效期验证</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-04-27</v>
+        <v>张三</v>
       </c>
       <c r="E117" t="str">
-        <v>致命</v>
+        <v>2026-04-23</v>
       </c>
       <c r="F117" t="str">
-        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险。已经定位到问题根因，是由于异步请求时序问题导致状态不一致。预计解决时间：2026-05-03</v>
+        <v>一般</v>
+      </c>
+      <c r="G117" t="str">
+        <v>涉及第三方SDK兼容性问题，需要联系供应商获取技术支持</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B118" t="str">
         <v>T-BUG-037</v>
       </c>
-      <c r="B118" t="str">
+      <c r="C118" t="str">
         <v>用户列表页面在小屏幕设备上样式错乱，表格列重叠，需要优化响应式布局和媒体查询设置</v>
       </c>
-      <c r="C118" t="str">
-        <v>黄五</v>
-      </c>
       <c r="D118" t="str">
+        <v>林四</v>
+      </c>
+      <c r="E118" t="str">
         <v>2026-04-29</v>
       </c>
-      <c r="E118" t="str">
-        <v>严重</v>
-      </c>
       <c r="F118" t="str">
-        <v>该问题已在测试环境复现，正在编写修复方案</v>
+        <v>一般</v>
+      </c>
+      <c r="G118" t="str">
+        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B119" t="str">
         <v>T-BUG-038</v>
       </c>
-      <c r="B119" t="str">
-        <v>代码冗余严重，多个组件存在重复逻辑，需要抽取公共组件和工具函数，提高代码复用率</v>
-      </c>
       <c r="C119" t="str">
-        <v>黄五</v>
+        <v>首页加载性能问题严重，首屏渲染时间超过5秒，需要优化图片压缩、开启懒加载和代码分割</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-04-29</v>
+        <v>王五</v>
       </c>
       <c r="E119" t="str">
-        <v>提示</v>
+        <v>2026-04-28</v>
       </c>
       <c r="F119" t="str">
-        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-03</v>
+        <v>一般</v>
+      </c>
+      <c r="G119" t="str">
+        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险。该问题已在测试环境复现，正在编写修复方案。预计解决时间：2026-05-04</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B120" t="str">
         <v>T-BUG-039</v>
       </c>
-      <c r="B120" t="str">
-        <v>用户注册API接口返回400错误，参数验证失败，需要检查请求参数格式和后端验证逻辑是否匹配</v>
-      </c>
       <c r="C120" t="str">
-        <v>黄五</v>
+        <v>登录页面在Safari浏览器中点击登录按钮后崩溃，控制台显示TypeError: Cannot read properties of undefined，需要检查auth模块的用户信息获取逻辑是否有边界条件处理</v>
       </c>
       <c r="D120" t="str">
+        <v>王五</v>
+      </c>
+      <c r="E120" t="str">
         <v>2026-04-26</v>
       </c>
-      <c r="E120" t="str">
+      <c r="F120" t="str">
         <v>提示</v>
       </c>
-      <c r="F120" t="str">
-        <v>需要升级依赖库版本，但可能影响其他模块，需要评估风险。涉及第三方SDK兼容性问题，需要联系供应商获取技术支持。预计解决时间：2026-05-03</v>
+      <c r="G120" t="str">
+        <v>【deferred】需要升级依赖库版本，但可能影响其他模块，需要评估风险。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-06</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
+        <v>打开</v>
+      </c>
+      <c r="B121" t="str">
         <v>T-BUG-040</v>
       </c>
-      <c r="B121" t="str">
-        <v>API接口文档缺失，前端开发需要频繁询问后端字段含义，需要补充完整的接口文档</v>
-      </c>
       <c r="C121" t="str">
+        <v>代码冗余严重，多个组件存在重复逻辑，需要抽取公共组件和工具函数，提高代码复用率</v>
+      </c>
+      <c r="D121" t="str">
         <v>周九</v>
       </c>
-      <c r="D121" t="str">
-        <v>2026-05-01</v>
-      </c>
       <c r="E121" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="F121" t="str">
         <v>提示</v>
       </c>
-      <c r="F121" t="str">
-        <v>【暂不处理】需要与产品确认需求细节，当前需求描述不够清晰。已修复并发布到测试环境，等待测试验证。预计解决时间：2026-05-03</v>
+      <c r="G121" t="str">
+        <v>该问题已在测试环境复现，正在编写修复方案</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="A3" r:id="rId2"/>
+    <hyperlink ref="A4" r:id="rId3"/>
+    <hyperlink ref="A5" r:id="rId4"/>
+    <hyperlink ref="A6" r:id="rId5"/>
+    <hyperlink ref="A7" r:id="rId6"/>
+    <hyperlink ref="A8" r:id="rId7"/>
+    <hyperlink ref="A9" r:id="rId8"/>
+    <hyperlink ref="A10" r:id="rId9"/>
+    <hyperlink ref="A11" r:id="rId10"/>
+    <hyperlink ref="A12" r:id="rId11"/>
+    <hyperlink ref="A13" r:id="rId12"/>
+    <hyperlink ref="A14" r:id="rId13"/>
+    <hyperlink ref="A15" r:id="rId14"/>
+    <hyperlink ref="A16" r:id="rId15"/>
+    <hyperlink ref="A17" r:id="rId16"/>
+    <hyperlink ref="A18" r:id="rId17"/>
+    <hyperlink ref="A19" r:id="rId18"/>
+    <hyperlink ref="A20" r:id="rId19"/>
+    <hyperlink ref="A21" r:id="rId20"/>
+    <hyperlink ref="A22" r:id="rId21"/>
+    <hyperlink ref="A23" r:id="rId22"/>
+    <hyperlink ref="A24" r:id="rId23"/>
+    <hyperlink ref="A25" r:id="rId24"/>
+    <hyperlink ref="A26" r:id="rId25"/>
+    <hyperlink ref="A27" r:id="rId26"/>
+    <hyperlink ref="A28" r:id="rId27"/>
+    <hyperlink ref="A29" r:id="rId28"/>
+    <hyperlink ref="A30" r:id="rId29"/>
+    <hyperlink ref="A31" r:id="rId30"/>
+    <hyperlink ref="A32" r:id="rId31"/>
+    <hyperlink ref="A33" r:id="rId32"/>
+    <hyperlink ref="A34" r:id="rId33"/>
+    <hyperlink ref="A35" r:id="rId34"/>
+    <hyperlink ref="A36" r:id="rId35"/>
+    <hyperlink ref="A37" r:id="rId36"/>
+    <hyperlink ref="A38" r:id="rId37"/>
+    <hyperlink ref="A39" r:id="rId38"/>
+    <hyperlink ref="A40" r:id="rId39"/>
+    <hyperlink ref="A41" r:id="rId40"/>
+    <hyperlink ref="A42" r:id="rId41"/>
+    <hyperlink ref="A43" r:id="rId42"/>
+    <hyperlink ref="A44" r:id="rId43"/>
+    <hyperlink ref="A45" r:id="rId44"/>
+    <hyperlink ref="A46" r:id="rId45"/>
+    <hyperlink ref="A47" r:id="rId46"/>
+    <hyperlink ref="A48" r:id="rId47"/>
+    <hyperlink ref="A49" r:id="rId48"/>
+    <hyperlink ref="A50" r:id="rId49"/>
+    <hyperlink ref="A51" r:id="rId50"/>
+    <hyperlink ref="A52" r:id="rId51"/>
+    <hyperlink ref="A53" r:id="rId52"/>
+    <hyperlink ref="A54" r:id="rId53"/>
+    <hyperlink ref="A55" r:id="rId54"/>
+    <hyperlink ref="A56" r:id="rId55"/>
+    <hyperlink ref="A57" r:id="rId56"/>
+    <hyperlink ref="A58" r:id="rId57"/>
+    <hyperlink ref="A59" r:id="rId58"/>
+    <hyperlink ref="A60" r:id="rId59"/>
+    <hyperlink ref="A61" r:id="rId60"/>
+    <hyperlink ref="A62" r:id="rId61"/>
+    <hyperlink ref="A63" r:id="rId62"/>
+    <hyperlink ref="A64" r:id="rId63"/>
+    <hyperlink ref="A65" r:id="rId64"/>
+    <hyperlink ref="A66" r:id="rId65"/>
+    <hyperlink ref="A67" r:id="rId66"/>
+    <hyperlink ref="A68" r:id="rId67"/>
+    <hyperlink ref="A69" r:id="rId68"/>
+    <hyperlink ref="A70" r:id="rId69"/>
+    <hyperlink ref="A71" r:id="rId70"/>
+    <hyperlink ref="A72" r:id="rId71"/>
+    <hyperlink ref="A73" r:id="rId72"/>
+    <hyperlink ref="A74" r:id="rId73"/>
+    <hyperlink ref="A75" r:id="rId74"/>
+    <hyperlink ref="A76" r:id="rId75"/>
+    <hyperlink ref="A77" r:id="rId76"/>
+    <hyperlink ref="A78" r:id="rId77"/>
+    <hyperlink ref="A79" r:id="rId78"/>
+    <hyperlink ref="A80" r:id="rId79"/>
+    <hyperlink ref="A81" r:id="rId80"/>
+    <hyperlink ref="A82" r:id="rId81"/>
+    <hyperlink ref="A83" r:id="rId82"/>
+    <hyperlink ref="A84" r:id="rId83"/>
+    <hyperlink ref="A85" r:id="rId84"/>
+    <hyperlink ref="A86" r:id="rId85"/>
+    <hyperlink ref="A87" r:id="rId86"/>
+    <hyperlink ref="A88" r:id="rId87"/>
+    <hyperlink ref="A89" r:id="rId88"/>
+    <hyperlink ref="A90" r:id="rId89"/>
+    <hyperlink ref="A91" r:id="rId90"/>
+    <hyperlink ref="A92" r:id="rId91"/>
+    <hyperlink ref="A93" r:id="rId92"/>
+    <hyperlink ref="A94" r:id="rId93"/>
+    <hyperlink ref="A95" r:id="rId94"/>
+    <hyperlink ref="A96" r:id="rId95"/>
+    <hyperlink ref="A97" r:id="rId96"/>
+    <hyperlink ref="A98" r:id="rId97"/>
+    <hyperlink ref="A99" r:id="rId98"/>
+    <hyperlink ref="A100" r:id="rId99"/>
+    <hyperlink ref="A101" r:id="rId100"/>
+    <hyperlink ref="A102" r:id="rId101"/>
+    <hyperlink ref="A103" r:id="rId102"/>
+    <hyperlink ref="A104" r:id="rId103"/>
+    <hyperlink ref="A105" r:id="rId104"/>
+    <hyperlink ref="A106" r:id="rId105"/>
+    <hyperlink ref="A107" r:id="rId106"/>
+    <hyperlink ref="A108" r:id="rId107"/>
+    <hyperlink ref="A109" r:id="rId108"/>
+    <hyperlink ref="A110" r:id="rId109"/>
+    <hyperlink ref="A111" r:id="rId110"/>
+    <hyperlink ref="A112" r:id="rId111"/>
+    <hyperlink ref="A113" r:id="rId112"/>
+    <hyperlink ref="A114" r:id="rId113"/>
+    <hyperlink ref="A115" r:id="rId114"/>
+    <hyperlink ref="A116" r:id="rId115"/>
+    <hyperlink ref="A117" r:id="rId116"/>
+    <hyperlink ref="A118" r:id="rId117"/>
+    <hyperlink ref="A119" r:id="rId118"/>
+    <hyperlink ref="A120" r:id="rId119"/>
+    <hyperlink ref="A121" r:id="rId120"/>
+  </hyperlinks>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F121"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G121"/>
   </ignoredErrors>
 </worksheet>
 </file>